--- a/Финансовый план.xlsx
+++ b/Финансовый план.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Личные финансы\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1203097-BAB3-47D3-9070-E02B4C9A4E24}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F238D8A8-D62D-4E46-AD67-E65A8AA651A6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="36727" windowHeight="20060" xr2:uid="{37FD5756-AF69-4080-8577-8AF04EAE00BB}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Движение денежных средств" sheetId="1" r:id="rId1"/>
     <sheet name="Баланс" sheetId="2" r:id="rId2"/>
     <sheet name="Зарплата" sheetId="3" r:id="rId3"/>
-    <sheet name="Такси" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -111,6 +110,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="T9" authorId="0" shapeId="0" xr:uid="{D0DF9B91-F5E9-4745-A0D0-A5844B2D8BEE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++подарки на праздники</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R13" authorId="0" shapeId="0" xr:uid="{5168E3D7-DA63-45ED-9B71-F1DABF15F85E}">
       <text>
         <r>
@@ -134,6 +159,32 @@
           </rPr>
           <t xml:space="preserve">
 Пересел с эконома на комфорт. Чаще ездил в час пик из-за плохой погоды</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V14" authorId="0" shapeId="0" xr:uid="{979D3938-9FAE-4BB3-A930-BF0EB44C3AD4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++2 забыл кошелек</t>
         </r>
       </text>
     </comment>
@@ -163,6 +214,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="T16" authorId="0" shapeId="0" xr:uid="{ED9878A8-D9D6-4397-877A-5DFBA0F731FC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++спортпит</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="P17" authorId="0" shapeId="0" xr:uid="{DEC318AC-9514-4B6A-820A-B5F816C73FD8}">
       <text>
         <r>
@@ -215,6 +292,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="V18" authorId="0" shapeId="0" xr:uid="{AB83BD70-7B11-4B2B-B79A-C282CC671F43}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+в конце мая перестал готовить</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V20" authorId="0" shapeId="0" xr:uid="{BB34642C-AD30-4DEB-86E8-7D73BAD6FF2A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++ накопился капремонт</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R25" authorId="0" shapeId="0" xr:uid="{BCB6E9DC-55FC-4AB1-8C44-92EC56568579}">
       <text>
         <r>
@@ -267,6 +396,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="T26" authorId="0" shapeId="0" xr:uid="{213023F7-BBDE-48FB-A5E1-1A2156DD3B01}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++др Егора</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="P35" authorId="0" shapeId="0" xr:uid="{8490D096-1DD1-4102-BC38-7E9D4D2F6337}">
       <text>
         <r>
@@ -290,6 +445,32 @@
           </rPr>
           <t xml:space="preserve">
 добавил мяч и бутсы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T35" authorId="0" shapeId="0" xr:uid="{0A3A52CD-C235-49CC-8A3F-4C2787F77007}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++одежда на осень и зиму в дереню</t>
         </r>
       </text>
     </comment>
@@ -319,6 +500,59 @@
         </r>
       </text>
     </comment>
+    <comment ref="T43" authorId="0" shapeId="0" xr:uid="{B188542D-BA4D-4FD0-8D4E-D3CE0337B586}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++сломалась плита</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T45" authorId="0" shapeId="0" xr:uid="{C678F5AF-E024-4D17-A949-2CA890935911}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
++горнолыжка
++музлото</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R46" authorId="0" shapeId="0" xr:uid="{FE30266C-1108-48F5-B4F5-3D960918C498}">
       <text>
         <r>
@@ -342,6 +576,32 @@
           </rPr>
           <t xml:space="preserve">
 +Футбол</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V46" authorId="0" shapeId="0" xr:uid="{B6A81519-EFC5-4341-AE09-D1286D0E95F4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Пользователь:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Загранпаспорт</t>
         </r>
       </text>
     </comment>
@@ -751,7 +1011,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="108">
   <si>
     <t>Кат 1</t>
   </si>
@@ -933,21 +1193,9 @@
     <t>Развлечения</t>
   </si>
   <si>
-    <t>Альфа от 25 февр</t>
-  </si>
-  <si>
-    <t>Альфа от 25 мая</t>
-  </si>
-  <si>
-    <t>ВТБ от 25 июля</t>
-  </si>
-  <si>
     <t>Открытие ИИС</t>
   </si>
   <si>
-    <t>Альфа Капитал от 27 июля</t>
-  </si>
-  <si>
     <t>план</t>
   </si>
   <si>
@@ -957,9 +1205,6 @@
     <t>ИИС</t>
   </si>
   <si>
-    <t>сентябрь</t>
-  </si>
-  <si>
     <t>Счета</t>
   </si>
   <si>
@@ -1053,12 +1298,6 @@
     <t>3. Итогова сумма на конец зимы 1 221 061. Риск не получить 200 000 премии остаюется</t>
   </si>
   <si>
-    <t>декабрь</t>
-  </si>
-  <si>
-    <t>Альфа Капитал от 9 сентября</t>
-  </si>
-  <si>
     <t>Альфа ежедневный (до 26к)</t>
   </si>
   <si>
@@ -1080,25 +1319,22 @@
     <t>Имущество</t>
   </si>
   <si>
-    <t>Минут</t>
-  </si>
-  <si>
-    <t>Цена</t>
-  </si>
-  <si>
-    <t>Год</t>
-  </si>
-  <si>
-    <t>Стоимсость минуты</t>
-  </si>
-  <si>
-    <t>Прирост</t>
-  </si>
-  <si>
-    <t>Стоимость минуты</t>
-  </si>
-  <si>
     <t>Коррекция</t>
+  </si>
+  <si>
+    <t>март</t>
+  </si>
+  <si>
+    <t>Айнур</t>
+  </si>
+  <si>
+    <t>Альфа-Капитал Золото</t>
+  </si>
+  <si>
+    <t>Альфа-Капитал Российские облигации</t>
+  </si>
+  <si>
+    <t>Альфа от 28 февр</t>
   </si>
 </sst>
 </file>
@@ -1108,12 +1344,28 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1306,7 +1558,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1648,19 +1900,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1793,277 +2032,301 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="8" xfId="11" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="9" xfId="11" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="12" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="10" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" xfId="10" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="10" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="10" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="9" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="12" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="12" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="12" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="5" xfId="12" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="12" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="5" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="8" xfId="11" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="9" xfId="11" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="12" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="10" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="10" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="10" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="10" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="12" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="2" xfId="12" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="4" xfId="12" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" xfId="12" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" xfId="12" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="6" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="7" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="11" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="4" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="3" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="14" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="6" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="7" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="11" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="4" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="3" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="16" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="14" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="21" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="16" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="22" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="19" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="24" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="21" xfId="10" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="29" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="22" xfId="10" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="29" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="30" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="18" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="24" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="18" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="24" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="24" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="16" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="12" borderId="9" xfId="11" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="12" borderId="21" xfId="11" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="12" borderId="16" xfId="11" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="18" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="24" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="17" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="25" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="26" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="23" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="12" borderId="22" xfId="11" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="17" xfId="4" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="10" xfId="4" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="19" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="17" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="20" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="9" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="21" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="22" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="17" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="22" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="33" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="2" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="18" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="24" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="18" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="24" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="2" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="24" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="21" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="16" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="17" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="9" xfId="11" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="21" xfId="11" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="16" xfId="11" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="18" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="24" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="17" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="25" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="26" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="23" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="22" xfId="11" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="17" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="10" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="19" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="0" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="17" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="10" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="20" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="9" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="21" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="22" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="17" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="20" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="22" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="2" borderId="32" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="6" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="11" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="0" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="6" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="29" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="12" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="13" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="2" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="29" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="13" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="6" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="11" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="0" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="6" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="2" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="33" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="31" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="33" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="14" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="33" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="14" xfId="11" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="4" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="31" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="31" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="33" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="35" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="25" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="16" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="36" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="24" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="27" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="8" xfId="11" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="1" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="4" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="37" xfId="12" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="12" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="15" xfId="9" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="28" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="30" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="30" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="30" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="38" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="28" xfId="9" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="39" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="27" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="15" xfId="9" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="27" xfId="9" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="29" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="6" xfId="8" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="29" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="28" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="40" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="6" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="28" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="31" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="37" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="34" xfId="4" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="32" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="34" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="14" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="35" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="34" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="14" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="12" borderId="14" xfId="11" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="32" xfId="4" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="32" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="32" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="34" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="36" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="25" xfId="5" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="16" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="37" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="24" xfId="4" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="16" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="8" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="41" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="12" borderId="8" xfId="11" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="1" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="4" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="13" borderId="38" xfId="12" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="39" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="40" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="12" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="41" xfId="9" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="5" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="27" xfId="9" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="42" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2359,7 +2622,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="G1:T66"/>
+  <dimension ref="G1:X66"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
@@ -2368,2208 +2631,2975 @@
     <col min="8" max="8" width="6.42578125" customWidth="1"/>
     <col min="9" max="9" width="6.5703125" customWidth="1"/>
     <col min="10" max="10" width="17.140625" customWidth="1"/>
-    <col min="11" max="15" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="18" width="9.140625" customWidth="1"/>
+    <col min="19" max="20" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="7:20" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G1" s="146" t="s">
+    <row r="1" spans="7:24" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="186" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="146" t="s">
+      <c r="H1" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="186" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="147" t="s">
+      <c r="J1" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="64">
+      <c r="K1" s="61">
         <v>2024</v>
       </c>
-      <c r="L1" s="192">
+      <c r="L1" s="181">
         <v>2025</v>
       </c>
-      <c r="M1" s="192"/>
-      <c r="N1" s="192"/>
-      <c r="O1" s="192"/>
-      <c r="P1" s="192"/>
-      <c r="Q1" s="192"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="63">
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="197">
         <v>2026</v>
       </c>
-    </row>
-    <row r="2" spans="7:20" x14ac:dyDescent="0.25">
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="155" t="s">
-        <v>71</v>
-      </c>
-      <c r="L2" s="156"/>
-      <c r="M2" s="155" t="s">
-        <v>107</v>
-      </c>
-      <c r="N2" s="156"/>
-      <c r="O2" s="148" t="s">
+      <c r="U1" s="198"/>
+      <c r="V1" s="198"/>
+      <c r="W1" s="198"/>
+      <c r="X1" s="199"/>
+    </row>
+    <row r="2" spans="7:24" x14ac:dyDescent="0.25">
+      <c r="G2" s="186"/>
+      <c r="H2" s="186"/>
+      <c r="I2" s="186"/>
+      <c r="J2" s="187"/>
+      <c r="K2" s="179" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="180"/>
+      <c r="M2" s="179" t="s">
+        <v>100</v>
+      </c>
+      <c r="N2" s="180"/>
+      <c r="O2" s="188" t="s">
         <v>56</v>
       </c>
-      <c r="P2" s="197"/>
-      <c r="Q2" s="199" t="s">
-        <v>70</v>
-      </c>
-      <c r="R2" s="144"/>
-      <c r="S2" s="143" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="144"/>
-    </row>
-    <row r="3" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="P2" s="189"/>
+      <c r="Q2" s="185" t="s">
+        <v>65</v>
+      </c>
+      <c r="R2" s="184"/>
+      <c r="S2" s="183" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="184"/>
+      <c r="U2" s="179" t="s">
+        <v>100</v>
+      </c>
+      <c r="V2" s="180"/>
+      <c r="W2" s="196" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" s="180"/>
+    </row>
+    <row r="3" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G3" s="25" t="s">
         <v>39</v>
       </c>
       <c r="H3" s="26"/>
       <c r="I3" s="26"/>
       <c r="J3" s="26"/>
-      <c r="K3" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="L3" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="P3" s="182" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q3" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="R3" s="62" t="s">
-        <v>66</v>
-      </c>
-      <c r="S3" s="61" t="s">
-        <v>65</v>
-      </c>
-      <c r="T3" s="62" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="K3" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="O3" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="P3" s="161" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="T3" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="U3" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="V3" s="60" t="s">
+        <v>62</v>
+      </c>
+      <c r="W3" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="X3" s="60" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G4" s="27"/>
       <c r="H4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="157"/>
-      <c r="L4" s="178">
+      <c r="K4" s="136"/>
+      <c r="L4" s="157">
         <f t="shared" ref="L4:N4" si="0">SUM(L5,L9)</f>
         <v>676249</v>
       </c>
-      <c r="M4" s="157"/>
-      <c r="N4" s="178">
+      <c r="M4" s="136"/>
+      <c r="N4" s="157">
         <f t="shared" si="0"/>
         <v>500858</v>
       </c>
-      <c r="O4" s="99">
+      <c r="O4" s="96">
         <f t="shared" ref="O4:P4" si="1">SUM(O5,O9)</f>
         <v>551727</v>
       </c>
-      <c r="P4" s="154">
+      <c r="P4" s="135">
         <f t="shared" si="1"/>
         <v>651542</v>
       </c>
-      <c r="Q4" s="99">
+      <c r="Q4" s="96">
         <f t="shared" ref="Q4:R4" si="2">SUM(Q5,Q9)</f>
         <v>599500</v>
       </c>
-      <c r="R4" s="100">
+      <c r="R4" s="97">
         <f t="shared" si="2"/>
         <v>621406</v>
       </c>
-      <c r="S4" s="99">
+      <c r="S4" s="96">
         <f t="shared" ref="S4:T4" si="3">SUM(S5,S9)</f>
         <v>612450</v>
       </c>
-      <c r="T4" s="100">
+      <c r="T4" s="97">
         <f t="shared" si="3"/>
+        <v>671669</v>
+      </c>
+      <c r="U4" s="96">
+        <f t="shared" ref="U4:V4" si="4">SUM(U5,U9)</f>
+        <v>497000</v>
+      </c>
+      <c r="V4" s="97">
+        <f t="shared" si="4"/>
+        <v>515817</v>
+      </c>
+      <c r="W4" s="96">
+        <f t="shared" ref="W4:X4" si="5">SUM(W5,W9)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X4" s="97">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G5" s="27"/>
       <c r="H5" s="3"/>
       <c r="I5" s="16" t="s">
         <v>31</v>
       </c>
       <c r="J5" s="17"/>
-      <c r="K5" s="158"/>
-      <c r="L5" s="69">
+      <c r="K5" s="137"/>
+      <c r="L5" s="66">
         <f>SUM(L6:L8)</f>
         <v>674858</v>
       </c>
-      <c r="M5" s="158"/>
-      <c r="N5" s="69">
+      <c r="M5" s="137"/>
+      <c r="N5" s="66">
         <f>SUM(N6:N8)</f>
         <v>499729</v>
       </c>
-      <c r="O5" s="68">
-        <f t="shared" ref="O5:T5" si="4">SUM(O6:O8)</f>
+      <c r="O5" s="65">
+        <f t="shared" ref="O5:T5" si="6">SUM(O6:O8)</f>
         <v>550327</v>
       </c>
-      <c r="P5" s="67">
-        <f t="shared" si="4"/>
+      <c r="P5" s="64">
+        <f t="shared" si="6"/>
         <v>629535</v>
       </c>
-      <c r="Q5" s="68">
-        <f t="shared" si="4"/>
+      <c r="Q5" s="65">
+        <f t="shared" si="6"/>
         <v>598000</v>
       </c>
-      <c r="R5" s="101">
-        <f t="shared" si="4"/>
+      <c r="R5" s="98">
+        <f t="shared" si="6"/>
         <v>614289</v>
       </c>
-      <c r="S5" s="68">
-        <f t="shared" si="4"/>
+      <c r="S5" s="65">
+        <f t="shared" si="6"/>
         <v>607450</v>
       </c>
-      <c r="T5" s="101">
-        <f t="shared" si="4"/>
+      <c r="T5" s="98">
+        <f t="shared" si="6"/>
+        <v>654523</v>
+      </c>
+      <c r="U5" s="65">
+        <f t="shared" ref="U5:V5" si="7">SUM(U6:U8)</f>
+        <v>495000</v>
+      </c>
+      <c r="V5" s="98">
+        <f t="shared" si="7"/>
+        <v>512017</v>
+      </c>
+      <c r="W5" s="65">
+        <f t="shared" ref="W5:X5" si="8">SUM(W6:W8)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X5" s="98">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G6" s="27"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="159"/>
-      <c r="L6" s="173">
+      <c r="K6" s="138"/>
+      <c r="L6" s="152">
         <f>152858+205648+83072</f>
         <v>441578</v>
       </c>
-      <c r="M6" s="159"/>
-      <c r="N6" s="173">
+      <c r="M6" s="138"/>
+      <c r="N6" s="152">
         <f>161109+182619+146701</f>
         <v>490429</v>
       </c>
-      <c r="O6" s="103">
+      <c r="O6" s="100">
         <v>483327</v>
       </c>
-      <c r="P6" s="102">
+      <c r="P6" s="99">
         <f>143786+100857+64181+126009+50230+21527+39296</f>
         <v>545886</v>
       </c>
-      <c r="Q6" s="103">
+      <c r="Q6" s="100">
         <f>593000</f>
         <v>593000</v>
       </c>
-      <c r="R6" s="104">
+      <c r="R6" s="101">
         <f>73350+130820+86107+78932+67515+82520+34780+43808</f>
         <v>597832</v>
       </c>
-      <c r="S6" s="103">
+      <c r="S6" s="100">
         <f>45820+7495+82450+43973+120923+86789</f>
         <v>387450</v>
       </c>
-      <c r="T6" s="104"/>
-    </row>
-    <row r="7" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T6" s="101">
+        <f>45844+77427+44010+121028+86863</f>
+        <v>375172</v>
+      </c>
+      <c r="U6" s="100">
+        <v>480000</v>
+      </c>
+      <c r="V6" s="101">
+        <f>78176+74268+82519+82520+82520+82519</f>
+        <v>482522</v>
+      </c>
+      <c r="W6" s="100"/>
+      <c r="X6" s="101"/>
+    </row>
+    <row r="7" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G7" s="27"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="159"/>
-      <c r="L7" s="173">
+      <c r="K7" s="138"/>
+      <c r="L7" s="152">
         <f>213864+19416</f>
         <v>233280</v>
       </c>
-      <c r="M7" s="159"/>
-      <c r="N7" s="173">
+      <c r="M7" s="138"/>
+      <c r="N7" s="152">
         <v>9300</v>
       </c>
-      <c r="O7" s="103"/>
-      <c r="P7" s="102">
+      <c r="O7" s="100"/>
+      <c r="P7" s="99">
         <f>16193</f>
         <v>16193</v>
       </c>
-      <c r="Q7" s="103">
+      <c r="Q7" s="100">
         <v>5000</v>
       </c>
-      <c r="R7" s="104">
+      <c r="R7" s="101">
         <v>16457</v>
       </c>
-      <c r="S7" s="103">
+      <c r="S7" s="100">
         <f>200000+20000</f>
         <v>220000</v>
       </c>
-      <c r="T7" s="104"/>
-    </row>
-    <row r="8" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T7" s="101">
+        <f>7328+80623+191400</f>
+        <v>279351</v>
+      </c>
+      <c r="U7" s="100">
+        <v>15000</v>
+      </c>
+      <c r="V7" s="101">
+        <f>29495</f>
+        <v>29495</v>
+      </c>
+      <c r="W7" s="100"/>
+      <c r="X7" s="101"/>
+    </row>
+    <row r="8" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G8" s="27"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="49" t="s">
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="159"/>
-      <c r="L8" s="173"/>
-      <c r="M8" s="159"/>
-      <c r="N8" s="173"/>
-      <c r="O8" s="103">
+      <c r="K8" s="138"/>
+      <c r="L8" s="152"/>
+      <c r="M8" s="138"/>
+      <c r="N8" s="152"/>
+      <c r="O8" s="100">
         <v>67000</v>
       </c>
-      <c r="P8" s="132">
+      <c r="P8" s="129">
         <f>18880+48576</f>
         <v>67456</v>
       </c>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="105"/>
-      <c r="S8" s="103"/>
-      <c r="T8" s="105"/>
-    </row>
-    <row r="9" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="Q8" s="100"/>
+      <c r="R8" s="102"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="100"/>
+      <c r="V8" s="102"/>
+      <c r="W8" s="100"/>
+      <c r="X8" s="102"/>
+    </row>
+    <row r="9" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G9" s="27"/>
       <c r="H9" s="4"/>
       <c r="I9" s="33" t="s">
         <v>47</v>
       </c>
       <c r="J9" s="34"/>
-      <c r="K9" s="160"/>
-      <c r="L9" s="174">
+      <c r="K9" s="139"/>
+      <c r="L9" s="153">
         <f>647+744</f>
         <v>1391</v>
       </c>
-      <c r="M9" s="160"/>
-      <c r="N9" s="174">
+      <c r="M9" s="139"/>
+      <c r="N9" s="153">
         <f>788+341</f>
         <v>1129</v>
       </c>
-      <c r="O9" s="107">
+      <c r="O9" s="104">
         <v>1400</v>
       </c>
-      <c r="P9" s="106">
+      <c r="P9" s="103">
         <f>302+13000+7719+395+521+70</f>
         <v>22007</v>
       </c>
-      <c r="Q9" s="107">
+      <c r="Q9" s="104">
         <v>1500</v>
       </c>
-      <c r="R9" s="108">
+      <c r="R9" s="105">
         <f>1006+2306+175+1055+222+1332+377+644</f>
         <v>7117</v>
       </c>
-      <c r="S9" s="107">
+      <c r="S9" s="104">
         <v>5000</v>
       </c>
-      <c r="T9" s="108"/>
-    </row>
-    <row r="10" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T9" s="105">
+        <f>521+6500+596+682+3000+2615+192+72+1018+715+85+1150</f>
+        <v>17146</v>
+      </c>
+      <c r="U9" s="104">
+        <v>2000</v>
+      </c>
+      <c r="V9" s="105">
+        <f>883+135+153+749+107+317+528+88+840</f>
+        <v>3800</v>
+      </c>
+      <c r="W9" s="104"/>
+      <c r="X9" s="105"/>
+    </row>
+    <row r="10" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G10" s="27"/>
       <c r="H10" s="5" t="s">
         <v>36</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="74">
+      <c r="K10" s="70"/>
+      <c r="L10" s="71">
         <f>SUM(L11,L15,L19,L24,L27,L33,L36,L40,L43,L44,L45,L46)</f>
         <v>335963</v>
       </c>
-      <c r="M10" s="73"/>
-      <c r="N10" s="74">
+      <c r="M10" s="70"/>
+      <c r="N10" s="71">
         <f>SUM(N11,N15,N19,N24,N27,N33,N36,N40,N43,N44,N45,N46)</f>
         <v>205094</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="113">
         <f>SUM(O11,O15,O19,O24,O27,O33,O36,O40,O59,O43,O45,O46)</f>
         <v>211275</v>
       </c>
-      <c r="P10" s="75">
+      <c r="P10" s="72">
         <f>SUM(P11,P15,P19,P24,P27,P33,P36,P40,P43,P44,P45,P46)</f>
         <v>241439</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="113">
         <f>SUM(Q11,Q15,Q19,Q24,Q27,Q33,Q36,Q40,Q59,Q43,Q45,Q46)</f>
         <v>155810</v>
       </c>
-      <c r="R10" s="74">
+      <c r="R10" s="71">
         <f>SUM(R11,R15,R19,R24,R27,R33,R36,R40,R43,R44,R45,R46)</f>
         <v>280476</v>
       </c>
-      <c r="S10" s="74">
+      <c r="S10" s="71">
         <f>SUM(S11,S15,S19,S24,S27,S33,S36,S40,S43,S44,S45,S46)</f>
         <v>180410</v>
       </c>
-      <c r="T10" s="92">
-        <f>SUM(T11,T15,T19,T24,T27,T33,T36,T40,T43,T46)</f>
+      <c r="T10" s="71">
+        <f>SUM(T11,T15,T19,T24,T27,T33,T36,T40,T43,T44,T45,T46)</f>
+        <v>218570</v>
+      </c>
+      <c r="U10" s="71">
+        <f>SUM(U11,U15,U19,U24,U27,U33,U36,U40,U43,U44,U45,U46)</f>
+        <v>217950</v>
+      </c>
+      <c r="V10" s="71">
+        <f>SUM(V11,V15,V19,V24,V27,V33,V36,V40,V43,V44,V45,V46)</f>
+        <v>216397</v>
+      </c>
+      <c r="W10" s="71">
+        <f>SUM(W11,W15,W19,W24,W27,W33,W36,W40,W43,W44,W45,W46)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X10" s="71">
+        <f>SUM(X11,X15,X19,X24,X27,X33,X36,X40,X43,X44,X45,X46)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G11" s="27"/>
       <c r="H11" s="7"/>
       <c r="I11" s="14" t="s">
         <v>4</v>
       </c>
       <c r="J11" s="15"/>
-      <c r="K11" s="161"/>
-      <c r="L11" s="78">
-        <f t="shared" ref="L11:N11" si="5">SUM(L12:L14)</f>
+      <c r="K11" s="140"/>
+      <c r="L11" s="75">
+        <f t="shared" ref="L11:N11" si="9">SUM(L12:L14)</f>
         <v>12064</v>
       </c>
-      <c r="M11" s="161"/>
-      <c r="N11" s="78">
-        <f t="shared" si="5"/>
+      <c r="M11" s="140"/>
+      <c r="N11" s="75">
+        <f t="shared" si="9"/>
         <v>14975</v>
       </c>
-      <c r="O11" s="77">
-        <f t="shared" ref="O11:P11" si="6">SUM(O12:O14)</f>
+      <c r="O11" s="74">
+        <f t="shared" ref="O11:P11" si="10">SUM(O12:O14)</f>
         <v>14100</v>
       </c>
-      <c r="P11" s="76">
-        <f t="shared" si="6"/>
+      <c r="P11" s="73">
+        <f t="shared" si="10"/>
         <v>14557</v>
       </c>
-      <c r="Q11" s="77">
-        <f t="shared" ref="Q11:R11" si="7">SUM(Q12:Q14)</f>
+      <c r="Q11" s="74">
+        <f t="shared" ref="Q11:R11" si="11">SUM(Q12:Q14)</f>
         <v>14500</v>
       </c>
-      <c r="R11" s="94">
-        <f t="shared" si="7"/>
+      <c r="R11" s="91">
+        <f t="shared" si="11"/>
         <v>15304</v>
       </c>
-      <c r="S11" s="77">
-        <f t="shared" ref="S11:T11" si="8">SUM(S12:S14)</f>
+      <c r="S11" s="74">
+        <f t="shared" ref="S11:T11" si="12">SUM(S12:S14)</f>
         <v>13000</v>
       </c>
-      <c r="T11" s="94">
-        <f t="shared" si="8"/>
+      <c r="T11" s="91">
+        <f t="shared" si="12"/>
+        <v>14141</v>
+      </c>
+      <c r="U11" s="74">
+        <f t="shared" ref="U11:V11" si="13">SUM(U12:U14)</f>
+        <v>17000</v>
+      </c>
+      <c r="V11" s="91">
+        <f t="shared" si="13"/>
+        <v>17229</v>
+      </c>
+      <c r="W11" s="74">
+        <f t="shared" ref="W11:X11" si="14">SUM(W12:W14)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X11" s="91">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G12" s="27"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="122" t="s">
+      <c r="J12" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="162"/>
-      <c r="L12" s="176">
+      <c r="K12" s="141"/>
+      <c r="L12" s="155">
         <f>2394+1806+2212</f>
         <v>6412</v>
       </c>
-      <c r="M12" s="162"/>
-      <c r="N12" s="175">
+      <c r="M12" s="141"/>
+      <c r="N12" s="154">
         <f>1935+1763+1677</f>
         <v>5375</v>
       </c>
-      <c r="O12" s="110">
+      <c r="O12" s="107">
         <v>5900</v>
       </c>
-      <c r="P12" s="109">
+      <c r="P12" s="106">
         <f>1462+1376+1548+344+172+43</f>
         <v>4945</v>
       </c>
-      <c r="Q12" s="110">
+      <c r="Q12" s="107">
         <v>5000</v>
       </c>
-      <c r="R12" s="97">
+      <c r="R12" s="94">
         <f>115*43</f>
         <v>4945</v>
       </c>
-      <c r="S12" s="110">
+      <c r="S12" s="107">
         <v>5000</v>
       </c>
-      <c r="T12" s="97"/>
-    </row>
-    <row r="13" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T12" s="94">
+        <f>43*49+46*36+46*63</f>
+        <v>6661</v>
+      </c>
+      <c r="U12" s="107">
+        <v>6000</v>
+      </c>
+      <c r="V12" s="94">
+        <f>183*46</f>
+        <v>8418</v>
+      </c>
+      <c r="W12" s="107"/>
+      <c r="X12" s="94"/>
+    </row>
+    <row r="13" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G13" s="27"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
       <c r="J13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="162"/>
-      <c r="L13" s="175">
+      <c r="K13" s="141"/>
+      <c r="L13" s="154">
         <f>3007+503+310</f>
         <v>3820</v>
       </c>
-      <c r="M13" s="162"/>
-      <c r="N13" s="175">
+      <c r="M13" s="141"/>
+      <c r="N13" s="154">
         <f>1662+1290+1625</f>
         <v>4577</v>
       </c>
-      <c r="O13" s="110">
+      <c r="O13" s="107">
         <v>4100</v>
       </c>
-      <c r="P13" s="109">
+      <c r="P13" s="106">
         <f>4620</f>
         <v>4620</v>
       </c>
-      <c r="Q13" s="110">
+      <c r="Q13" s="107">
         <v>4500</v>
       </c>
-      <c r="R13" s="97">
+      <c r="R13" s="94">
         <f>326+284+389+272+264+361+305+333+352+159+163+543+353+353+289+216+216+339+314</f>
         <v>5831</v>
       </c>
-      <c r="S13" s="110">
+      <c r="S13" s="107">
         <v>6000</v>
       </c>
-      <c r="T13" s="97"/>
-    </row>
-    <row r="14" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T13" s="94">
+        <f>543+353+353+289+216+339+314+243+211+778+788+369+347+254</f>
+        <v>5397</v>
+      </c>
+      <c r="U13" s="107">
+        <v>6000</v>
+      </c>
+      <c r="V13" s="94">
+        <v>1683</v>
+      </c>
+      <c r="W13" s="107"/>
+      <c r="X13" s="94"/>
+    </row>
+    <row r="14" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G14" s="27"/>
       <c r="H14" s="7"/>
       <c r="I14" s="8"/>
       <c r="J14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="162"/>
-      <c r="L14" s="175">
+      <c r="K14" s="141"/>
+      <c r="L14" s="154">
         <f>469+1363</f>
         <v>1832</v>
       </c>
-      <c r="M14" s="162"/>
-      <c r="N14" s="175">
+      <c r="M14" s="141"/>
+      <c r="N14" s="154">
         <f>1821+1380+1822</f>
         <v>5023</v>
       </c>
-      <c r="O14" s="110">
+      <c r="O14" s="107">
         <v>4100</v>
       </c>
-      <c r="P14" s="109">
+      <c r="P14" s="106">
         <f>906+469+469+469+884+884+469+442</f>
         <v>4992</v>
       </c>
-      <c r="Q14" s="110">
+      <c r="Q14" s="107">
         <v>5000</v>
       </c>
-      <c r="R14" s="97">
+      <c r="R14" s="94">
         <f>442+442+442+469+442+469+442+469+442+469</f>
         <v>4528</v>
       </c>
-      <c r="S14" s="110">
+      <c r="S14" s="107">
         <v>2000</v>
       </c>
-      <c r="T14" s="97"/>
-    </row>
-    <row r="15" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T14" s="94">
+        <f>537+537+537+472</f>
+        <v>2083</v>
+      </c>
+      <c r="U14" s="107">
+        <v>5000</v>
+      </c>
+      <c r="V14" s="94">
+        <f>472+537+537+472+537+472+537+472+537+537+537+472+537+472</f>
+        <v>7128</v>
+      </c>
+      <c r="W14" s="107"/>
+      <c r="X14" s="94"/>
+    </row>
+    <row r="15" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G15" s="27"/>
       <c r="H15" s="7"/>
       <c r="I15" s="14" t="s">
         <v>8</v>
       </c>
       <c r="J15" s="15"/>
-      <c r="K15" s="161"/>
-      <c r="L15" s="78">
-        <f t="shared" ref="L15:N15" si="9">SUM(L16:L18)</f>
+      <c r="K15" s="140"/>
+      <c r="L15" s="75">
+        <f t="shared" ref="L15:N15" si="15">SUM(L16:L18)</f>
         <v>87438</v>
       </c>
-      <c r="M15" s="161"/>
-      <c r="N15" s="78">
-        <f t="shared" si="9"/>
+      <c r="M15" s="140"/>
+      <c r="N15" s="75">
+        <f t="shared" si="15"/>
         <v>66254</v>
       </c>
-      <c r="O15" s="77">
-        <f t="shared" ref="O15:T15" si="10">SUM(O16:O18)</f>
+      <c r="O15" s="74">
+        <f t="shared" ref="O15:T15" si="16">SUM(O16:O18)</f>
         <v>78000</v>
       </c>
-      <c r="P15" s="76">
-        <f t="shared" si="10"/>
+      <c r="P15" s="73">
+        <f t="shared" si="16"/>
         <v>88695</v>
       </c>
-      <c r="Q15" s="77">
-        <f t="shared" si="10"/>
+      <c r="Q15" s="74">
+        <f t="shared" si="16"/>
         <v>83000</v>
       </c>
-      <c r="R15" s="94">
-        <f t="shared" si="10"/>
+      <c r="R15" s="91">
+        <f t="shared" si="16"/>
         <v>69467</v>
       </c>
-      <c r="S15" s="77">
-        <f t="shared" si="10"/>
+      <c r="S15" s="74">
+        <f t="shared" si="16"/>
         <v>73000</v>
       </c>
-      <c r="T15" s="94">
-        <f t="shared" si="10"/>
+      <c r="T15" s="91">
+        <f t="shared" si="16"/>
+        <v>42817</v>
+      </c>
+      <c r="U15" s="74">
+        <f t="shared" ref="U15:V15" si="17">SUM(U16:U18)</f>
+        <v>45000</v>
+      </c>
+      <c r="V15" s="91">
+        <f t="shared" si="17"/>
+        <v>41557</v>
+      </c>
+      <c r="W15" s="74">
+        <f t="shared" ref="W15:X15" si="18">SUM(W16:W18)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X15" s="91">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G16" s="27"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="122" t="s">
-        <v>91</v>
-      </c>
-      <c r="K16" s="163"/>
-      <c r="L16" s="176">
+      <c r="J16" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="K16" s="142"/>
+      <c r="L16" s="155">
         <f>18503+11849+10369</f>
         <v>40721</v>
       </c>
-      <c r="M16" s="163"/>
-      <c r="N16" s="176">
+      <c r="M16" s="142"/>
+      <c r="N16" s="155">
         <f>10734+11259+6537</f>
         <v>28530</v>
       </c>
-      <c r="O16" s="110">
+      <c r="O16" s="107">
         <v>35000</v>
       </c>
-      <c r="P16" s="109">
+      <c r="P16" s="106">
         <f>7305+160+408+334+600+2040+150+339+80+561+160+120+130+275+610+305+266+250+92+73+420+150+407+619+350+160+7510+100+440+346+80+1304+80+150+170+70+173+400+994+480+166+1176+387+140+1139+150+247</f>
         <v>32066</v>
       </c>
-      <c r="Q16" s="110">
+      <c r="Q16" s="107">
         <v>35000</v>
       </c>
-      <c r="R16" s="124">
+      <c r="R16" s="121">
         <f>1163+130+80+173+30+200+450+139+80+780+210+150+100+136+126+65+90+123+254+90+170+580+90+121+80+863+245+80+12080+80+254+40+80+85+80+140+65+70+80+65+62+175+125+80+814+390+139+140+94+70+90+104+240+220+110+95+80+284+95+94+420</f>
         <v>23838</v>
       </c>
-      <c r="S16" s="110">
+      <c r="S16" s="107">
         <v>25000</v>
       </c>
-      <c r="T16" s="97"/>
-    </row>
-    <row r="17" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T16" s="94">
+        <f>85+130+100+539+281+104+73+60+380+59+428+200+120+213+332+226+456+188+234+423+1129+150+683+139+27+100+420+330+330+63+843+691+696+696+857+606+102+535+565+877</f>
+        <v>14470</v>
+      </c>
+      <c r="U16" s="107">
+        <v>15000</v>
+      </c>
+      <c r="V16" s="94">
+        <f>9159+855+853+2341</f>
+        <v>13208</v>
+      </c>
+      <c r="W16" s="107"/>
+      <c r="X16" s="94"/>
+    </row>
+    <row r="17" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G17" s="27"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
       <c r="J17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="162"/>
-      <c r="L17" s="175">
+      <c r="K17" s="141"/>
+      <c r="L17" s="154">
         <f>10470+14130+11479</f>
         <v>36079</v>
       </c>
-      <c r="M17" s="162"/>
-      <c r="N17" s="175">
+      <c r="M17" s="141"/>
+      <c r="N17" s="154">
         <f>10345+9069+5402</f>
         <v>24816</v>
       </c>
-      <c r="O17" s="110">
+      <c r="O17" s="107">
         <v>31000</v>
       </c>
-      <c r="P17" s="109">
+      <c r="P17" s="106">
         <f>3245+838+654+1120+550+530+360+250+498+1044+400+1530+852+1147+2919+100+500+490+663+1772+640+480+200+807+350+250+11320+485+947+300+2400+800+950+1849+470+480+550+570+85+581+125+838+676+310+220+230+1049</f>
         <v>47424</v>
       </c>
-      <c r="Q17" s="110">
+      <c r="Q17" s="107">
         <v>30000</v>
       </c>
-      <c r="R17" s="97">
+      <c r="R17" s="94">
         <f>520+500+230+230+815+1573+2630+230+1080+2680+450+420+150+1175+270+954+550+320+740+550+250+500+480</f>
         <v>17297</v>
       </c>
-      <c r="S17" s="110">
+      <c r="S17" s="107">
         <v>20000</v>
       </c>
-      <c r="T17" s="97"/>
-    </row>
-    <row r="18" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T17" s="94">
+        <f>150+150+250+1180+1120+748+150+500+320+700+600+370+753+860+200+2093+700+500+1741+504+2260+2820+1100+3790+1570+248</f>
+        <v>25377</v>
+      </c>
+      <c r="U17" s="107">
+        <v>25000</v>
+      </c>
+      <c r="V17" s="94">
+        <f>370+500+1629+1100+500+191+1210+267+267+327+500+150+267+1712+825+496+300+134+3550+3830+300+700+308+285+676</f>
+        <v>20394</v>
+      </c>
+      <c r="W17" s="107"/>
+      <c r="X17" s="94"/>
+    </row>
+    <row r="18" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G18" s="27"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="65" t="s">
+      <c r="J18" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="162"/>
-      <c r="L18" s="175">
+      <c r="K18" s="141"/>
+      <c r="L18" s="154">
         <f>5776+590+4272</f>
         <v>10638</v>
       </c>
-      <c r="M18" s="162"/>
-      <c r="N18" s="175">
+      <c r="M18" s="141"/>
+      <c r="N18" s="154">
         <f>5234+4121+3553</f>
         <v>12908</v>
       </c>
-      <c r="O18" s="110">
+      <c r="O18" s="107">
         <v>12000</v>
       </c>
-      <c r="P18" s="109">
+      <c r="P18" s="106">
         <f>908+100+475+147+176+118+226+295+182+438+212+304+191+376+250+192+294+1102+480+90+269+278+454+80+143+258+242+165+225+280+255</f>
         <v>9205</v>
       </c>
-      <c r="Q18" s="110">
+      <c r="Q18" s="107">
         <v>18000</v>
       </c>
-      <c r="R18" s="97">
+      <c r="R18" s="94">
         <f>165+223+207+145+359+134+480+225+165+260+224+237+838+537+215+283+85+225+195+520+250+195+324+145+243+290+80+185+383+379+480+251+292+135+253+198+176+285+330+193+237+480+186+309+265+202+403+310+250+208+250+173+250+263+224+238+237+480+250+85+195+154+173+580+141+182+140+250+244+152+574+210+480+245+138+203+250+636+259+438+250+181+375+140+223+280+445+371+327+390+143+87+480+250+400+250+206+149+150+289+483+189+410+131</f>
         <v>28332</v>
       </c>
-      <c r="S18" s="110">
+      <c r="S18" s="107">
         <v>28000</v>
       </c>
-      <c r="T18" s="97"/>
-    </row>
-    <row r="19" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T18" s="94">
+        <f>168+548+250+250+370+215+217+12+300+165+145+80+250</f>
+        <v>2970</v>
+      </c>
+      <c r="U18" s="107">
+        <v>5000</v>
+      </c>
+      <c r="V18" s="94">
+        <f>80+80+80+325+140+450+80+279+504+650+290+310+80+290+500+390+485+485+500+460+87+475+485+270+180</f>
+        <v>7955</v>
+      </c>
+      <c r="W18" s="107"/>
+      <c r="X18" s="94"/>
+    </row>
+    <row r="19" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G19" s="27"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="194" t="s">
-        <v>108</v>
+      <c r="I19" s="171" t="s">
+        <v>101</v>
       </c>
       <c r="J19" s="15"/>
-      <c r="K19" s="161"/>
-      <c r="L19" s="78">
-        <f t="shared" ref="L19" si="11">SUM(L20:L23)</f>
+      <c r="K19" s="140"/>
+      <c r="L19" s="75">
+        <f t="shared" ref="L19" si="19">SUM(L20:L23)</f>
         <v>45731</v>
       </c>
-      <c r="M19" s="161"/>
-      <c r="N19" s="78">
-        <f t="shared" ref="N19:T19" si="12">SUM(N20:N23)</f>
+      <c r="M19" s="140"/>
+      <c r="N19" s="75">
+        <f t="shared" ref="N19:T19" si="20">SUM(N20:N23)</f>
         <v>20758</v>
       </c>
-      <c r="O19" s="77">
-        <f t="shared" si="12"/>
+      <c r="O19" s="74">
+        <f t="shared" si="20"/>
         <v>19000</v>
       </c>
-      <c r="P19" s="76">
-        <f t="shared" si="12"/>
+      <c r="P19" s="73">
+        <f t="shared" si="20"/>
         <v>19412</v>
       </c>
-      <c r="Q19" s="77">
-        <f t="shared" si="12"/>
+      <c r="Q19" s="74">
+        <f t="shared" si="20"/>
         <v>20500</v>
       </c>
-      <c r="R19" s="94">
-        <f t="shared" si="12"/>
+      <c r="R19" s="91">
+        <f t="shared" si="20"/>
         <v>28408</v>
       </c>
-      <c r="S19" s="77">
-        <f t="shared" si="12"/>
+      <c r="S19" s="74">
+        <f t="shared" si="20"/>
         <v>37500</v>
       </c>
-      <c r="T19" s="94">
-        <f t="shared" si="12"/>
+      <c r="T19" s="91">
+        <f t="shared" si="20"/>
+        <v>41454</v>
+      </c>
+      <c r="U19" s="74">
+        <f t="shared" ref="U19:V19" si="21">SUM(U20:U23)</f>
+        <v>25000</v>
+      </c>
+      <c r="V19" s="91">
+        <f t="shared" si="21"/>
+        <v>34987</v>
+      </c>
+      <c r="W19" s="74">
+        <f t="shared" ref="W19:X19" si="22">SUM(W20:W23)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X19" s="91">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G20" s="27"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="K20" s="163"/>
-      <c r="L20" s="176">
+      <c r="K20" s="142"/>
+      <c r="L20" s="155">
         <f>6034+6424+5654</f>
         <v>18112</v>
       </c>
-      <c r="M20" s="163"/>
-      <c r="N20" s="176">
+      <c r="M20" s="142"/>
+      <c r="N20" s="155">
         <f>6987+6168+6304</f>
         <v>19459</v>
       </c>
-      <c r="O20" s="110">
+      <c r="O20" s="107">
         <v>19000</v>
       </c>
-      <c r="P20" s="109">
+      <c r="P20" s="106">
         <f>4456+4731+1329+4579</f>
         <v>15095</v>
       </c>
-      <c r="Q20" s="110">
+      <c r="Q20" s="107">
         <v>16500</v>
       </c>
-      <c r="R20" s="97">
+      <c r="R20" s="94">
         <f>6008+5250+3873</f>
         <v>15131</v>
       </c>
-      <c r="S20" s="110">
+      <c r="S20" s="107">
         <v>18500</v>
       </c>
-      <c r="T20" s="97"/>
-    </row>
-    <row r="21" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T20" s="94">
+        <f>6375+6946+8152</f>
+        <v>21473</v>
+      </c>
+      <c r="U20" s="107">
+        <v>20000</v>
+      </c>
+      <c r="V20" s="94">
+        <f>9456+7977+3843+6900+549</f>
+        <v>28725</v>
+      </c>
+      <c r="W20" s="107"/>
+      <c r="X20" s="94"/>
+    </row>
+    <row r="21" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G21" s="27"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="K21" s="162"/>
-      <c r="L21" s="175">
+      <c r="K21" s="141"/>
+      <c r="L21" s="154">
         <f>10076+3250+925</f>
         <v>14251</v>
       </c>
-      <c r="M21" s="162"/>
-      <c r="N21" s="175">
+      <c r="M21" s="141"/>
+      <c r="N21" s="154">
         <v>1299</v>
       </c>
-      <c r="O21" s="110"/>
-      <c r="P21" s="109">
+      <c r="O21" s="107"/>
+      <c r="P21" s="106">
         <f>1044+85+301+2641+246</f>
         <v>4317</v>
       </c>
-      <c r="Q21" s="110">
+      <c r="Q21" s="107">
         <v>4000</v>
       </c>
-      <c r="R21" s="97">
+      <c r="R21" s="94">
         <f>238+143+120+1361+230+910+807+210+168+854+520+1380</f>
         <v>6941</v>
       </c>
-      <c r="S21" s="110">
+      <c r="S21" s="107">
         <v>4000</v>
       </c>
-      <c r="T21" s="97"/>
-    </row>
-    <row r="22" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T21" s="94">
+        <f>288+236+1006+1006+240+385+390+629+272+523+261+2783</f>
+        <v>8019</v>
+      </c>
+      <c r="U21" s="107">
+        <v>5000</v>
+      </c>
+      <c r="V21" s="94">
+        <f>4675+80+549+737+221</f>
+        <v>6262</v>
+      </c>
+      <c r="W21" s="107"/>
+      <c r="X21" s="94"/>
+    </row>
+    <row r="22" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G22" s="27"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="122" t="s">
+      <c r="J22" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="K22" s="162"/>
-      <c r="L22" s="175">
+      <c r="K22" s="141"/>
+      <c r="L22" s="154">
         <f>12190</f>
         <v>12190</v>
       </c>
-      <c r="M22" s="162"/>
-      <c r="N22" s="175"/>
-      <c r="O22" s="110"/>
-      <c r="P22" s="109"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="97"/>
-      <c r="S22" s="110">
+      <c r="M22" s="141"/>
+      <c r="N22" s="154"/>
+      <c r="O22" s="107"/>
+      <c r="P22" s="106"/>
+      <c r="Q22" s="107"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="107">
         <v>15000</v>
       </c>
-      <c r="T22" s="97"/>
-    </row>
-    <row r="23" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T22" s="94">
+        <v>11962</v>
+      </c>
+      <c r="U22" s="107"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="107"/>
+      <c r="X22" s="94"/>
+    </row>
+    <row r="23" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G23" s="27"/>
       <c r="H23" s="7"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="123" t="s">
-        <v>90</v>
-      </c>
-      <c r="K23" s="164"/>
-      <c r="L23" s="177">
+      <c r="J23" s="120" t="s">
+        <v>85</v>
+      </c>
+      <c r="K23" s="143"/>
+      <c r="L23" s="156">
         <f>1178</f>
         <v>1178</v>
       </c>
-      <c r="M23" s="164"/>
-      <c r="N23" s="177"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="109"/>
-      <c r="Q23" s="96"/>
-      <c r="R23" s="97">
+      <c r="M23" s="143"/>
+      <c r="N23" s="156"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="106"/>
+      <c r="Q23" s="93"/>
+      <c r="R23" s="94">
         <v>6336</v>
       </c>
-      <c r="S23" s="96"/>
-      <c r="T23" s="97"/>
-    </row>
-    <row r="24" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="S23" s="93"/>
+      <c r="T23" s="94"/>
+      <c r="U23" s="93"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="93"/>
+      <c r="X23" s="94"/>
+    </row>
+    <row r="24" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G24" s="27"/>
       <c r="H24" s="7"/>
       <c r="I24" s="14" t="s">
         <v>16</v>
       </c>
       <c r="J24" s="15"/>
-      <c r="K24" s="161"/>
-      <c r="L24" s="78">
-        <f t="shared" ref="L24:N24" si="13">SUM(L25:L26)</f>
+      <c r="K24" s="140"/>
+      <c r="L24" s="75">
+        <f t="shared" ref="L24:N24" si="23">SUM(L25:L26)</f>
         <v>94570</v>
       </c>
-      <c r="M24" s="161"/>
-      <c r="N24" s="78">
-        <f t="shared" si="13"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="75">
+        <f t="shared" si="23"/>
         <v>87362</v>
       </c>
-      <c r="O24" s="77">
-        <f t="shared" ref="O24:P24" si="14">SUM(O25:O26)</f>
+      <c r="O24" s="74">
+        <f t="shared" ref="O24:P24" si="24">SUM(O25:O26)</f>
         <v>68600</v>
       </c>
-      <c r="P24" s="76">
-        <f t="shared" si="14"/>
+      <c r="P24" s="73">
+        <f t="shared" si="24"/>
         <v>59401</v>
       </c>
-      <c r="Q24" s="77">
-        <f t="shared" ref="Q24:R24" si="15">SUM(Q25:Q26)</f>
+      <c r="Q24" s="74">
+        <f t="shared" ref="Q24:R24" si="25">SUM(Q25:Q26)</f>
         <v>10000</v>
       </c>
-      <c r="R24" s="94">
-        <f t="shared" si="15"/>
+      <c r="R24" s="91">
+        <f t="shared" si="25"/>
         <v>77269</v>
       </c>
-      <c r="S24" s="77">
-        <f t="shared" ref="S24:T24" si="16">SUM(S25:S26)</f>
+      <c r="S24" s="74">
+        <f t="shared" ref="S24:T24" si="26">SUM(S25:S26)</f>
         <v>12000</v>
       </c>
-      <c r="T24" s="94">
-        <f t="shared" si="16"/>
+      <c r="T24" s="91">
+        <f t="shared" si="26"/>
+        <v>18480</v>
+      </c>
+      <c r="U24" s="74">
+        <f t="shared" ref="U24:V24" si="27">SUM(U25:U26)</f>
+        <v>30000</v>
+      </c>
+      <c r="V24" s="91">
+        <f t="shared" si="27"/>
+        <v>34200</v>
+      </c>
+      <c r="W24" s="74">
+        <f t="shared" ref="W24:X24" si="28">SUM(W25:W26)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X24" s="91">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G25" s="27"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K25" s="162"/>
-      <c r="L25" s="175">
+      <c r="K25" s="141"/>
+      <c r="L25" s="154">
         <f>20000+22500+25770</f>
         <v>68270</v>
       </c>
-      <c r="M25" s="162"/>
-      <c r="N25" s="175">
+      <c r="M25" s="141"/>
+      <c r="N25" s="154">
         <f>22000+15000+25255</f>
         <v>62255</v>
       </c>
-      <c r="O25" s="110">
+      <c r="O25" s="107">
         <v>65000</v>
       </c>
-      <c r="P25" s="109">
+      <c r="P25" s="106">
         <f>10000+10000+5000+1100+5000+10000</f>
         <v>41100</v>
       </c>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="97">
+      <c r="Q25" s="107"/>
+      <c r="R25" s="94">
         <v>68500</v>
       </c>
-      <c r="S25" s="110">
+      <c r="S25" s="107">
         <v>10000</v>
       </c>
-      <c r="T25" s="97"/>
-    </row>
-    <row r="26" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T25" s="94">
+        <f>4471+109+8900</f>
+        <v>13480</v>
+      </c>
+      <c r="U25" s="107">
+        <v>20000</v>
+      </c>
+      <c r="V25" s="94">
+        <f>6030+15000+5000</f>
+        <v>26030</v>
+      </c>
+      <c r="W25" s="107"/>
+      <c r="X25" s="94"/>
+    </row>
+    <row r="26" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G26" s="27"/>
       <c r="H26" s="7"/>
       <c r="I26" s="8"/>
       <c r="J26" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="K26" s="164"/>
-      <c r="L26" s="177">
+      <c r="K26" s="143"/>
+      <c r="L26" s="156">
         <f>19857+6443</f>
         <v>26300</v>
       </c>
-      <c r="M26" s="164"/>
-      <c r="N26" s="177">
+      <c r="M26" s="143"/>
+      <c r="N26" s="156">
         <f>18618+2889+3600</f>
         <v>25107</v>
       </c>
-      <c r="O26" s="96">
+      <c r="O26" s="93">
         <v>3600</v>
       </c>
-      <c r="P26" s="109">
+      <c r="P26" s="106">
         <f>6750+149+2000+9402</f>
         <v>18301</v>
       </c>
-      <c r="Q26" s="96">
+      <c r="Q26" s="93">
         <v>10000</v>
       </c>
-      <c r="R26" s="97">
+      <c r="R26" s="94">
         <v>8769</v>
       </c>
-      <c r="S26" s="96">
+      <c r="S26" s="93">
         <v>2000</v>
       </c>
-      <c r="T26" s="97"/>
-    </row>
-    <row r="27" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T26" s="94">
+        <f>5000</f>
+        <v>5000</v>
+      </c>
+      <c r="U26" s="93">
+        <v>10000</v>
+      </c>
+      <c r="V26" s="94">
+        <f>3170+5000</f>
+        <v>8170</v>
+      </c>
+      <c r="W26" s="93"/>
+      <c r="X26" s="94"/>
+    </row>
+    <row r="27" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G27" s="27"/>
       <c r="H27" s="7"/>
       <c r="I27" s="21" t="s">
         <v>29</v>
       </c>
       <c r="J27" s="11"/>
-      <c r="K27" s="165"/>
-      <c r="L27" s="82">
-        <f t="shared" ref="L27:N27" si="17">SUM(L28:L32)</f>
+      <c r="K27" s="144"/>
+      <c r="L27" s="79">
+        <f t="shared" ref="L27:N27" si="29">SUM(L28:L32)</f>
         <v>7570</v>
       </c>
-      <c r="M27" s="165"/>
-      <c r="N27" s="82">
-        <f t="shared" si="17"/>
+      <c r="M27" s="144"/>
+      <c r="N27" s="79">
+        <f t="shared" si="29"/>
         <v>9999</v>
       </c>
-      <c r="O27" s="81">
-        <f t="shared" ref="O27:P27" si="18">SUM(O28:O32)</f>
+      <c r="O27" s="78">
+        <f t="shared" ref="O27:P27" si="30">SUM(O28:O32)</f>
         <v>4320</v>
       </c>
-      <c r="P27" s="76">
-        <f t="shared" si="18"/>
+      <c r="P27" s="73">
+        <f t="shared" si="30"/>
         <v>3780</v>
       </c>
-      <c r="Q27" s="81">
-        <f t="shared" ref="Q27:R27" si="19">SUM(Q28:Q32)</f>
+      <c r="Q27" s="78">
+        <f t="shared" ref="Q27:R27" si="31">SUM(Q28:Q32)</f>
         <v>2610</v>
       </c>
-      <c r="R27" s="94">
-        <f t="shared" si="19"/>
+      <c r="R27" s="91">
+        <f t="shared" si="31"/>
         <v>2728</v>
       </c>
-      <c r="S27" s="81">
-        <f t="shared" ref="S27:T27" si="20">SUM(S28:S32)</f>
+      <c r="S27" s="78">
+        <f t="shared" ref="S27:T27" si="32">SUM(S28:S32)</f>
         <v>2610</v>
       </c>
-      <c r="T27" s="94">
-        <f t="shared" si="20"/>
+      <c r="T27" s="91">
+        <f t="shared" si="32"/>
+        <v>6240</v>
+      </c>
+      <c r="U27" s="78">
+        <f t="shared" ref="U27:V27" si="33">SUM(U28:U32)</f>
+        <v>13350</v>
+      </c>
+      <c r="V27" s="91">
+        <f t="shared" si="33"/>
+        <v>8424</v>
+      </c>
+      <c r="W27" s="78">
+        <f t="shared" ref="W27:X27" si="34">SUM(W28:W32)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X27" s="91">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G28" s="27"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="K28" s="162"/>
-      <c r="L28" s="175">
+      <c r="K28" s="141"/>
+      <c r="L28" s="154">
         <f>900+900+900</f>
         <v>2700</v>
       </c>
-      <c r="M28" s="162"/>
-      <c r="N28" s="175">
+      <c r="M28" s="141"/>
+      <c r="N28" s="154">
         <f>900+300+450</f>
         <v>1650</v>
       </c>
-      <c r="O28" s="110">
+      <c r="O28" s="107">
         <v>1350</v>
       </c>
-      <c r="P28" s="109">
+      <c r="P28" s="106">
         <f>450+450+450</f>
         <v>1350</v>
       </c>
-      <c r="Q28" s="110">
+      <c r="Q28" s="107">
         <v>1350</v>
       </c>
-      <c r="R28" s="97">
+      <c r="R28" s="94">
         <f>450*3+118</f>
         <v>1468</v>
       </c>
-      <c r="S28" s="110">
+      <c r="S28" s="107">
         <v>1350</v>
       </c>
-      <c r="T28" s="97"/>
-    </row>
-    <row r="29" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T28" s="94">
+        <f>450+70+100+550</f>
+        <v>1170</v>
+      </c>
+      <c r="U28" s="107">
+        <v>1350</v>
+      </c>
+      <c r="V28" s="94">
+        <f>50+550+50+550+550</f>
+        <v>1750</v>
+      </c>
+      <c r="W28" s="107"/>
+      <c r="X28" s="94"/>
+    </row>
+    <row r="29" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G29" s="27"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K29" s="162"/>
-      <c r="L29" s="175"/>
-      <c r="M29" s="162"/>
-      <c r="N29" s="175">
+      <c r="K29" s="141"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="154">
         <f>3889</f>
         <v>3889</v>
       </c>
-      <c r="O29" s="110"/>
-      <c r="P29" s="109"/>
-      <c r="Q29" s="110"/>
-      <c r="R29" s="97"/>
-      <c r="S29" s="110"/>
-      <c r="T29" s="97"/>
-    </row>
-    <row r="30" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="O29" s="107"/>
+      <c r="P29" s="106"/>
+      <c r="Q29" s="107"/>
+      <c r="R29" s="94"/>
+      <c r="S29" s="107"/>
+      <c r="T29" s="94"/>
+      <c r="U29" s="107">
+        <v>4000</v>
+      </c>
+      <c r="V29" s="94"/>
+      <c r="W29" s="107"/>
+      <c r="X29" s="94"/>
+    </row>
+    <row r="30" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G30" s="27"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K30" s="162"/>
-      <c r="L30" s="175"/>
-      <c r="M30" s="162"/>
-      <c r="N30" s="175">
+      <c r="K30" s="141"/>
+      <c r="L30" s="154"/>
+      <c r="M30" s="141"/>
+      <c r="N30" s="154">
         <v>990</v>
       </c>
-      <c r="O30" s="110"/>
-      <c r="P30" s="109"/>
-      <c r="Q30" s="110"/>
-      <c r="R30" s="97"/>
-      <c r="S30" s="110"/>
-      <c r="T30" s="97"/>
-    </row>
-    <row r="31" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="O30" s="107"/>
+      <c r="P30" s="106"/>
+      <c r="Q30" s="107"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="107"/>
+      <c r="T30" s="94"/>
+      <c r="U30" s="107">
+        <v>1000</v>
+      </c>
+      <c r="V30" s="94">
+        <v>1599</v>
+      </c>
+      <c r="W30" s="107"/>
+      <c r="X30" s="94"/>
+    </row>
+    <row r="31" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G31" s="27"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="K31" s="163"/>
-      <c r="L31" s="176">
+      <c r="K31" s="142"/>
+      <c r="L31" s="155">
         <f>1700+1700+300</f>
         <v>3700</v>
       </c>
-      <c r="M31" s="163"/>
-      <c r="N31" s="176">
+      <c r="M31" s="142"/>
+      <c r="N31" s="155">
         <f>1700+300+300</f>
         <v>2300</v>
       </c>
-      <c r="O31" s="110">
+      <c r="O31" s="107">
         <v>1800</v>
       </c>
-      <c r="P31" s="109">
+      <c r="P31" s="106">
         <f>600+600</f>
         <v>1200</v>
       </c>
-      <c r="Q31" s="110"/>
-      <c r="R31" s="97"/>
-      <c r="S31" s="110"/>
-      <c r="T31" s="97"/>
-    </row>
-    <row r="32" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="Q31" s="107"/>
+      <c r="R31" s="94"/>
+      <c r="S31" s="107"/>
+      <c r="T31" s="94">
+        <f>1900+1900</f>
+        <v>3800</v>
+      </c>
+      <c r="U31" s="107">
+        <v>5700</v>
+      </c>
+      <c r="V31" s="94">
+        <f>1900+1900</f>
+        <v>3800</v>
+      </c>
+      <c r="W31" s="107"/>
+      <c r="X31" s="94"/>
+    </row>
+    <row r="32" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G32" s="27"/>
       <c r="H32" s="7"/>
       <c r="I32" s="8"/>
       <c r="J32" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="K32" s="164"/>
-      <c r="L32" s="177">
+      <c r="K32" s="143"/>
+      <c r="L32" s="156">
         <f>390+390+390</f>
         <v>1170</v>
       </c>
-      <c r="M32" s="164"/>
-      <c r="N32" s="177">
+      <c r="M32" s="143"/>
+      <c r="N32" s="156">
         <f>390+390+390</f>
         <v>1170</v>
       </c>
-      <c r="O32" s="96">
+      <c r="O32" s="93">
         <v>1170</v>
       </c>
-      <c r="P32" s="180">
+      <c r="P32" s="159">
         <f>390+420+420</f>
         <v>1230</v>
       </c>
-      <c r="Q32" s="96">
+      <c r="Q32" s="93">
         <v>1260</v>
       </c>
-      <c r="R32" s="111">
+      <c r="R32" s="108">
         <f>420*3</f>
         <v>1260</v>
       </c>
-      <c r="S32" s="96">
+      <c r="S32" s="93">
         <v>1260</v>
       </c>
-      <c r="T32" s="111"/>
-    </row>
-    <row r="33" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T32" s="108">
+        <f>420+425+425</f>
+        <v>1270</v>
+      </c>
+      <c r="U32" s="93">
+        <v>1300</v>
+      </c>
+      <c r="V32" s="108">
+        <f>425+425+425</f>
+        <v>1275</v>
+      </c>
+      <c r="W32" s="93"/>
+      <c r="X32" s="108"/>
+    </row>
+    <row r="33" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G33" s="27"/>
       <c r="H33" s="7"/>
       <c r="I33" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J33" s="15"/>
-      <c r="K33" s="161"/>
-      <c r="L33" s="78">
-        <f t="shared" ref="L33:N33" si="21">SUM(L34:L35)</f>
+      <c r="K33" s="140"/>
+      <c r="L33" s="75">
+        <f t="shared" ref="L33:N33" si="35">SUM(L34:L35)</f>
         <v>4672</v>
       </c>
-      <c r="M33" s="161"/>
-      <c r="N33" s="78">
-        <f t="shared" si="21"/>
+      <c r="M33" s="140"/>
+      <c r="N33" s="75">
+        <f t="shared" si="35"/>
         <v>1869</v>
       </c>
-      <c r="O33" s="77">
-        <f t="shared" ref="O33:P33" si="22">SUM(O34:O35)</f>
+      <c r="O33" s="74">
+        <f t="shared" ref="O33:P33" si="36">SUM(O34:O35)</f>
         <v>5812</v>
       </c>
-      <c r="P33" s="76">
-        <f t="shared" si="22"/>
+      <c r="P33" s="73">
+        <f t="shared" si="36"/>
         <v>14413</v>
       </c>
-      <c r="Q33" s="77">
-        <f t="shared" ref="Q33:R33" si="23">SUM(Q34:Q35)</f>
+      <c r="Q33" s="74">
+        <f t="shared" ref="Q33:R33" si="37">SUM(Q34:Q35)</f>
         <v>18200</v>
       </c>
-      <c r="R33" s="94">
-        <f t="shared" si="23"/>
+      <c r="R33" s="91">
+        <f t="shared" si="37"/>
         <v>23068</v>
       </c>
-      <c r="S33" s="77">
-        <f t="shared" ref="S33:T33" si="24">SUM(S34:S35)</f>
+      <c r="S33" s="74">
+        <f t="shared" ref="S33:T33" si="38">SUM(S34:S35)</f>
         <v>3200</v>
       </c>
-      <c r="T33" s="94">
-        <f t="shared" si="24"/>
+      <c r="T33" s="91">
+        <f t="shared" si="38"/>
+        <v>14801</v>
+      </c>
+      <c r="U33" s="74">
+        <f t="shared" ref="U33:V33" si="39">SUM(U34:U35)</f>
+        <v>18600</v>
+      </c>
+      <c r="V33" s="91">
+        <f t="shared" si="39"/>
+        <v>17575</v>
+      </c>
+      <c r="W33" s="74">
+        <f t="shared" ref="W33:X33" si="40">SUM(W34:W35)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X33" s="91">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G34" s="27"/>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="K34" s="162"/>
-      <c r="L34" s="175">
+      <c r="K34" s="141"/>
+      <c r="L34" s="154">
         <f>1600+1600</f>
         <v>3200</v>
       </c>
-      <c r="M34" s="162"/>
-      <c r="N34" s="175">
+      <c r="M34" s="141"/>
+      <c r="N34" s="154">
         <v>1600</v>
       </c>
-      <c r="O34" s="110">
+      <c r="O34" s="107">
         <v>3200</v>
       </c>
-      <c r="P34" s="109">
+      <c r="P34" s="106">
         <f>1600</f>
         <v>1600</v>
       </c>
-      <c r="Q34" s="110">
+      <c r="Q34" s="107">
         <v>3200</v>
       </c>
-      <c r="R34" s="124">
+      <c r="R34" s="121">
         <f>1600+1600</f>
         <v>3200</v>
       </c>
-      <c r="S34" s="110">
+      <c r="S34" s="107">
         <v>3200</v>
       </c>
-      <c r="T34" s="97"/>
-    </row>
-    <row r="35" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T34" s="94">
+        <f>1800+1800</f>
+        <v>3600</v>
+      </c>
+      <c r="U34" s="107">
+        <v>3600</v>
+      </c>
+      <c r="V34" s="94">
+        <f>1800+1800</f>
+        <v>3600</v>
+      </c>
+      <c r="W34" s="107"/>
+      <c r="X34" s="94"/>
+    </row>
+    <row r="35" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G35" s="27"/>
       <c r="H35" s="7"/>
       <c r="I35" s="8"/>
       <c r="J35" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="K35" s="162"/>
-      <c r="L35" s="175">
+      <c r="K35" s="141"/>
+      <c r="L35" s="154">
         <f>1472</f>
         <v>1472</v>
       </c>
-      <c r="M35" s="162"/>
-      <c r="N35" s="175">
+      <c r="M35" s="141"/>
+      <c r="N35" s="154">
         <v>269</v>
       </c>
-      <c r="O35" s="110">
+      <c r="O35" s="107">
         <v>2612</v>
       </c>
-      <c r="P35" s="95">
+      <c r="P35" s="92">
         <f>2448+807+3658+299+3600+2001</f>
         <v>12813</v>
       </c>
-      <c r="Q35" s="110">
+      <c r="Q35" s="107">
         <v>15000</v>
       </c>
-      <c r="R35" s="112">
+      <c r="R35" s="109">
         <f>276+1638+365+4612+6878+665+3839+1595</f>
         <v>19868</v>
       </c>
-      <c r="S35" s="110"/>
-      <c r="T35" s="112"/>
-    </row>
-    <row r="36" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="S35" s="107"/>
+      <c r="T35" s="109">
+        <f>6341+3140+1720</f>
+        <v>11201</v>
+      </c>
+      <c r="U35" s="107">
+        <v>15000</v>
+      </c>
+      <c r="V35" s="109">
+        <f>1609+908+5697+5222+539</f>
+        <v>13975</v>
+      </c>
+      <c r="W35" s="107"/>
+      <c r="X35" s="109"/>
+    </row>
+    <row r="36" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G36" s="27"/>
       <c r="H36" s="7"/>
       <c r="I36" s="14" t="s">
         <v>20</v>
       </c>
       <c r="J36" s="15"/>
-      <c r="K36" s="161"/>
-      <c r="L36" s="78">
-        <f t="shared" ref="L36:N36" si="25">SUM(L37:L39)</f>
+      <c r="K36" s="140"/>
+      <c r="L36" s="75">
+        <f t="shared" ref="L36:N36" si="41">SUM(L37:L39)</f>
         <v>7818</v>
       </c>
-      <c r="M36" s="161"/>
-      <c r="N36" s="78">
-        <f t="shared" si="25"/>
+      <c r="M36" s="140"/>
+      <c r="N36" s="75">
+        <f t="shared" si="41"/>
         <v>1012</v>
       </c>
-      <c r="O36" s="77">
-        <f t="shared" ref="O36:P36" si="26">SUM(O37:O39)</f>
+      <c r="O36" s="74">
+        <f t="shared" ref="O36:P36" si="42">SUM(O37:O39)</f>
         <v>1227</v>
       </c>
-      <c r="P36" s="76">
-        <f t="shared" si="26"/>
+      <c r="P36" s="73">
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="77">
-        <f t="shared" ref="Q36:R36" si="27">SUM(Q37:Q39)</f>
+      <c r="Q36" s="74">
+        <f t="shared" ref="Q36:R36" si="43">SUM(Q37:Q39)</f>
         <v>500</v>
       </c>
-      <c r="R36" s="94">
-        <f t="shared" si="27"/>
+      <c r="R36" s="91">
+        <f t="shared" si="43"/>
         <v>30299</v>
       </c>
-      <c r="S36" s="77">
-        <f t="shared" ref="S36:T36" si="28">SUM(S37:S39)</f>
+      <c r="S36" s="74">
+        <f t="shared" ref="S36:T36" si="44">SUM(S37:S39)</f>
         <v>7100</v>
       </c>
-      <c r="T36" s="94">
-        <f t="shared" si="28"/>
+      <c r="T36" s="91">
+        <f t="shared" si="44"/>
+        <v>608</v>
+      </c>
+      <c r="U36" s="74">
+        <f t="shared" ref="U36:V36" si="45">SUM(U37:U39)</f>
+        <v>6000</v>
+      </c>
+      <c r="V36" s="91">
+        <f t="shared" si="45"/>
+        <v>367</v>
+      </c>
+      <c r="W36" s="74">
+        <f t="shared" ref="W36:X36" si="46">SUM(W37:W39)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X36" s="91">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G37" s="27"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K37" s="162"/>
-      <c r="L37" s="175">
+      <c r="K37" s="141"/>
+      <c r="L37" s="154">
         <f>99+710+627</f>
         <v>1436</v>
       </c>
-      <c r="M37" s="162"/>
-      <c r="N37" s="175">
+      <c r="M37" s="141"/>
+      <c r="N37" s="154">
         <v>200</v>
       </c>
-      <c r="O37" s="110">
+      <c r="O37" s="107">
         <v>1227</v>
       </c>
-      <c r="P37" s="109"/>
-      <c r="Q37" s="110">
+      <c r="P37" s="106"/>
+      <c r="Q37" s="107">
         <v>500</v>
       </c>
-      <c r="R37" s="97"/>
-      <c r="S37" s="110">
+      <c r="R37" s="94"/>
+      <c r="S37" s="107">
         <v>1500</v>
       </c>
-      <c r="T37" s="97"/>
-    </row>
-    <row r="38" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T37" s="94">
+        <f>239</f>
+        <v>239</v>
+      </c>
+      <c r="U37" s="107">
+        <v>1000</v>
+      </c>
+      <c r="V37" s="94">
+        <f>237+130</f>
+        <v>367</v>
+      </c>
+      <c r="W37" s="107"/>
+      <c r="X37" s="94"/>
+    </row>
+    <row r="38" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G38" s="27"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K38" s="162"/>
-      <c r="L38" s="175">
+      <c r="K38" s="141"/>
+      <c r="L38" s="154">
         <f>5600</f>
         <v>5600</v>
       </c>
-      <c r="M38" s="162"/>
-      <c r="N38" s="175"/>
-      <c r="O38" s="110"/>
-      <c r="P38" s="109"/>
-      <c r="Q38" s="110"/>
-      <c r="R38" s="97"/>
-      <c r="S38" s="110">
+      <c r="M38" s="141"/>
+      <c r="N38" s="154"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="106"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="94"/>
+      <c r="S38" s="107">
         <v>5600</v>
       </c>
-      <c r="T38" s="97"/>
-    </row>
-    <row r="39" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T38" s="94"/>
+      <c r="U38" s="107">
+        <v>5000</v>
+      </c>
+      <c r="V38" s="94"/>
+      <c r="W38" s="107"/>
+      <c r="X38" s="94"/>
+    </row>
+    <row r="39" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G39" s="27"/>
       <c r="H39" s="7"/>
       <c r="I39" s="8"/>
       <c r="J39" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="K39" s="162"/>
-      <c r="L39" s="175">
+      <c r="K39" s="141"/>
+      <c r="L39" s="154">
         <f>782</f>
         <v>782</v>
       </c>
-      <c r="M39" s="162"/>
-      <c r="N39" s="175">
+      <c r="M39" s="141"/>
+      <c r="N39" s="154">
         <v>812</v>
       </c>
-      <c r="O39" s="110"/>
-      <c r="P39" s="95"/>
-      <c r="Q39" s="110"/>
-      <c r="R39" s="112">
+      <c r="O39" s="107"/>
+      <c r="P39" s="92"/>
+      <c r="Q39" s="107"/>
+      <c r="R39" s="109">
         <f>24864+2590+2402+443</f>
         <v>30299</v>
       </c>
-      <c r="S39" s="110"/>
-      <c r="T39" s="112"/>
-    </row>
-    <row r="40" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="S39" s="107"/>
+      <c r="T39" s="109">
+        <f>369</f>
+        <v>369</v>
+      </c>
+      <c r="U39" s="107"/>
+      <c r="V39" s="109"/>
+      <c r="W39" s="107"/>
+      <c r="X39" s="109"/>
+    </row>
+    <row r="40" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G40" s="27"/>
       <c r="H40" s="7"/>
       <c r="I40" s="21" t="s">
         <v>23</v>
       </c>
       <c r="J40" s="11"/>
-      <c r="K40" s="161"/>
-      <c r="L40" s="78">
-        <f t="shared" ref="L40:N40" si="29">SUM(L41:L42)</f>
+      <c r="K40" s="140"/>
+      <c r="L40" s="75">
+        <f t="shared" ref="L40:N40" si="47">SUM(L41:L42)</f>
         <v>27034</v>
       </c>
-      <c r="M40" s="161"/>
-      <c r="N40" s="78">
-        <f t="shared" si="29"/>
+      <c r="M40" s="140"/>
+      <c r="N40" s="75">
+        <f t="shared" si="47"/>
         <v>2113</v>
       </c>
-      <c r="O40" s="77">
-        <f t="shared" ref="O40:P40" si="30">SUM(O41:O42)</f>
+      <c r="O40" s="74">
+        <f t="shared" ref="O40:P40" si="48">SUM(O41:O42)</f>
         <v>16216</v>
       </c>
-      <c r="P40" s="76">
-        <f t="shared" si="30"/>
+      <c r="P40" s="73">
+        <f t="shared" si="48"/>
         <v>27354</v>
       </c>
-      <c r="Q40" s="77">
-        <f t="shared" ref="Q40:R40" si="31">SUM(Q41:Q42)</f>
+      <c r="Q40" s="74">
+        <f t="shared" ref="Q40:R40" si="49">SUM(Q41:Q42)</f>
         <v>1500</v>
       </c>
-      <c r="R40" s="94">
-        <f t="shared" si="31"/>
+      <c r="R40" s="91">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="S40" s="77">
-        <f t="shared" ref="S40:T40" si="32">SUM(S41:S42)</f>
+      <c r="S40" s="74">
+        <f t="shared" ref="S40:T40" si="50">SUM(S41:S42)</f>
         <v>1500</v>
       </c>
-      <c r="T40" s="94">
-        <f t="shared" si="32"/>
+      <c r="T40" s="91">
+        <f t="shared" si="50"/>
+        <v>3073</v>
+      </c>
+      <c r="U40" s="74">
+        <f t="shared" ref="U40:V40" si="51">SUM(U41:U42)</f>
+        <v>3000</v>
+      </c>
+      <c r="V40" s="91">
+        <f t="shared" si="51"/>
+        <v>5925</v>
+      </c>
+      <c r="W40" s="74">
+        <f t="shared" ref="W40:X40" si="52">SUM(W41:W42)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X40" s="91">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G41" s="27"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="162"/>
-      <c r="L41" s="175">
+      <c r="K41" s="141"/>
+      <c r="L41" s="154">
         <f>1467+817</f>
         <v>2284</v>
       </c>
-      <c r="M41" s="162"/>
-      <c r="N41" s="175">
+      <c r="M41" s="141"/>
+      <c r="N41" s="154">
         <v>2113</v>
       </c>
-      <c r="O41" s="110">
+      <c r="O41" s="107">
         <v>1466</v>
       </c>
-      <c r="P41" s="109">
+      <c r="P41" s="106">
         <f>1404</f>
         <v>1404</v>
       </c>
-      <c r="Q41" s="110">
+      <c r="Q41" s="107">
         <v>1500</v>
       </c>
-      <c r="R41" s="97"/>
-      <c r="S41" s="110">
+      <c r="R41" s="94"/>
+      <c r="S41" s="107">
         <v>1500</v>
       </c>
-      <c r="T41" s="97"/>
-    </row>
-    <row r="42" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T41" s="94">
+        <f>2748+325</f>
+        <v>3073</v>
+      </c>
+      <c r="U41" s="107">
+        <v>3000</v>
+      </c>
+      <c r="V41" s="94">
+        <f>649+902+286+404+1222+1496+966</f>
+        <v>5925</v>
+      </c>
+      <c r="W41" s="107"/>
+      <c r="X41" s="94"/>
+    </row>
+    <row r="42" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G42" s="27"/>
       <c r="H42" s="7"/>
       <c r="I42" s="8"/>
       <c r="J42" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K42" s="164"/>
-      <c r="L42" s="177">
+      <c r="K42" s="143"/>
+      <c r="L42" s="156">
         <f>24750</f>
         <v>24750</v>
       </c>
-      <c r="M42" s="164"/>
-      <c r="N42" s="177"/>
-      <c r="O42" s="96">
+      <c r="M42" s="143"/>
+      <c r="N42" s="156"/>
+      <c r="O42" s="93">
         <v>14750</v>
       </c>
-      <c r="P42" s="95">
+      <c r="P42" s="92">
         <f>25950</f>
         <v>25950</v>
       </c>
-      <c r="Q42" s="96"/>
-      <c r="R42" s="112"/>
-      <c r="S42" s="96"/>
-      <c r="T42" s="112"/>
-    </row>
-    <row r="43" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="Q42" s="93"/>
+      <c r="R42" s="109"/>
+      <c r="S42" s="93"/>
+      <c r="T42" s="109"/>
+      <c r="U42" s="93"/>
+      <c r="V42" s="109"/>
+      <c r="W42" s="93"/>
+      <c r="X42" s="109"/>
+    </row>
+    <row r="43" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G43" s="27"/>
       <c r="H43" s="7"/>
-      <c r="I43" s="51" t="s">
+      <c r="I43" s="50" t="s">
         <v>34</v>
       </c>
       <c r="J43" s="18"/>
-      <c r="K43" s="166"/>
-      <c r="L43" s="80">
+      <c r="K43" s="145"/>
+      <c r="L43" s="77">
         <f>18323+24000</f>
         <v>42323</v>
       </c>
-      <c r="M43" s="166"/>
-      <c r="N43" s="80"/>
-      <c r="O43" s="79"/>
-      <c r="P43" s="113"/>
-      <c r="Q43" s="79"/>
-      <c r="R43" s="114">
+      <c r="M43" s="145"/>
+      <c r="N43" s="77"/>
+      <c r="O43" s="76"/>
+      <c r="P43" s="110"/>
+      <c r="Q43" s="76"/>
+      <c r="R43" s="111">
         <v>6000</v>
       </c>
-      <c r="S43" s="79"/>
-      <c r="T43" s="114"/>
-    </row>
-    <row r="44" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="S43" s="76"/>
+      <c r="T43" s="111">
+        <v>20624</v>
+      </c>
+      <c r="U43" s="76">
+        <v>10000</v>
+      </c>
+      <c r="V43" s="111">
+        <f>295+335</f>
+        <v>630</v>
+      </c>
+      <c r="W43" s="76"/>
+      <c r="X43" s="111"/>
+    </row>
+    <row r="44" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G44" s="27"/>
       <c r="H44" s="7"/>
-      <c r="I44" s="125" t="s">
-        <v>92</v>
+      <c r="I44" s="122" t="s">
+        <v>87</v>
       </c>
       <c r="J44" s="18"/>
-      <c r="K44" s="166"/>
-      <c r="L44" s="80"/>
-      <c r="M44" s="166"/>
-      <c r="N44" s="80"/>
-      <c r="O44" s="79"/>
-      <c r="P44" s="113"/>
-      <c r="Q44" s="79"/>
-      <c r="R44" s="126">
+      <c r="K44" s="145"/>
+      <c r="L44" s="77"/>
+      <c r="M44" s="145"/>
+      <c r="N44" s="77"/>
+      <c r="O44" s="76"/>
+      <c r="P44" s="110"/>
+      <c r="Q44" s="76"/>
+      <c r="R44" s="123">
         <f>5000+2500+5000+2500+3000+5000+2500</f>
         <v>25500</v>
       </c>
-      <c r="S44" s="79">
+      <c r="S44" s="76">
         <v>25500</v>
       </c>
-      <c r="T44" s="114"/>
-    </row>
-    <row r="45" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T44" s="111">
+        <f>3000+1000+5000+2500+5000+2500+2500+2500+5000+5000+1000</f>
+        <v>35000</v>
+      </c>
+      <c r="U44" s="76">
+        <v>30000</v>
+      </c>
+      <c r="V44" s="111">
+        <v>43600</v>
+      </c>
+      <c r="W44" s="76"/>
+      <c r="X44" s="111"/>
+    </row>
+    <row r="45" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G45" s="27"/>
       <c r="H45" s="7"/>
-      <c r="I45" s="50" t="s">
+      <c r="I45" s="49" t="s">
         <v>59</v>
       </c>
       <c r="J45" s="11"/>
-      <c r="K45" s="165"/>
-      <c r="L45" s="82"/>
-      <c r="M45" s="165"/>
-      <c r="N45" s="82"/>
-      <c r="O45" s="81"/>
-      <c r="P45" s="181">
+      <c r="K45" s="144"/>
+      <c r="L45" s="79"/>
+      <c r="M45" s="144"/>
+      <c r="N45" s="79"/>
+      <c r="O45" s="78"/>
+      <c r="P45" s="160">
         <f>5500+700</f>
         <v>6200</v>
       </c>
-      <c r="Q45" s="81"/>
-      <c r="R45" s="115"/>
-      <c r="S45" s="81"/>
-      <c r="T45" s="115"/>
-    </row>
-    <row r="46" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="Q45" s="78"/>
+      <c r="R45" s="112"/>
+      <c r="S45" s="78"/>
+      <c r="T45" s="112">
+        <f>430+1580+1185+7090+2400</f>
+        <v>12685</v>
+      </c>
+      <c r="U45" s="78">
+        <v>10000</v>
+      </c>
+      <c r="V45" s="112"/>
+      <c r="W45" s="78"/>
+      <c r="X45" s="112"/>
+    </row>
+    <row r="46" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G46" s="27"/>
       <c r="H46" s="8"/>
       <c r="I46" s="32" t="s">
         <v>47</v>
       </c>
       <c r="J46" s="18"/>
-      <c r="K46" s="166"/>
-      <c r="L46" s="80">
+      <c r="K46" s="145"/>
+      <c r="L46" s="77">
         <f>4419+2124+200</f>
         <v>6743</v>
       </c>
-      <c r="M46" s="166"/>
-      <c r="N46" s="80">
+      <c r="M46" s="145"/>
+      <c r="N46" s="77">
         <v>752</v>
       </c>
-      <c r="O46" s="79">
+      <c r="O46" s="76">
         <v>4000</v>
       </c>
-      <c r="P46" s="76">
+      <c r="P46" s="73">
         <f>258+258+690+258+1750+199+150+52+288+440+950+150+84+2100</f>
         <v>7627</v>
       </c>
-      <c r="Q46" s="79">
+      <c r="Q46" s="76">
         <v>5000</v>
       </c>
-      <c r="R46" s="94">
+      <c r="R46" s="91">
         <f>98+300+200+300+250+50+150+240+370+150+150+175</f>
         <v>2433</v>
       </c>
-      <c r="S46" s="79">
+      <c r="S46" s="76">
         <v>5000</v>
       </c>
-      <c r="T46" s="94"/>
-    </row>
-    <row r="47" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T46" s="91">
+        <f>250+380+230+2398+270+270+325+9+50+300+340+128+65+375+40+30+25+25+9+100+1000+1800+2+176+50</f>
+        <v>8647</v>
+      </c>
+      <c r="U46" s="76">
+        <v>10000</v>
+      </c>
+      <c r="V46" s="91">
+        <f>380+350+450+85+225+185+620+225+300+200+790+410+565+64+6000+490+58+262+244</f>
+        <v>11903</v>
+      </c>
+      <c r="W46" s="76"/>
+      <c r="X46" s="91"/>
+    </row>
+    <row r="47" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G47" s="28"/>
       <c r="H47" s="22" t="s">
         <v>37</v>
       </c>
       <c r="I47" s="23"/>
       <c r="J47" s="23"/>
-      <c r="K47" s="167"/>
-      <c r="L47" s="85">
-        <f t="shared" ref="L47" si="33">L4-L10</f>
+      <c r="K47" s="146"/>
+      <c r="L47" s="82">
+        <f t="shared" ref="L47" si="53">L4-L10</f>
         <v>340286</v>
       </c>
-      <c r="M47" s="167"/>
-      <c r="N47" s="85">
-        <f t="shared" ref="N47:T47" si="34">N4-N10</f>
+      <c r="M47" s="146"/>
+      <c r="N47" s="82">
+        <f t="shared" ref="N47:T47" si="54">N4-N10</f>
         <v>295764</v>
       </c>
-      <c r="O47" s="84">
-        <f t="shared" si="34"/>
+      <c r="O47" s="81">
+        <f t="shared" si="54"/>
         <v>340452</v>
       </c>
-      <c r="P47" s="83">
-        <f t="shared" si="34"/>
+      <c r="P47" s="80">
+        <f t="shared" si="54"/>
         <v>410103</v>
       </c>
-      <c r="Q47" s="84">
-        <f t="shared" si="34"/>
+      <c r="Q47" s="81">
+        <f t="shared" si="54"/>
         <v>443690</v>
       </c>
-      <c r="R47" s="98">
-        <f t="shared" si="34"/>
+      <c r="R47" s="95">
+        <f t="shared" si="54"/>
         <v>340930</v>
       </c>
-      <c r="S47" s="84">
-        <f t="shared" si="34"/>
+      <c r="S47" s="81">
+        <f t="shared" si="54"/>
         <v>432040</v>
       </c>
-      <c r="T47" s="98">
-        <f t="shared" si="34"/>
+      <c r="T47" s="95">
+        <f t="shared" si="54"/>
+        <v>453099</v>
+      </c>
+      <c r="U47" s="81">
+        <f t="shared" ref="U47:V47" si="55">U4-U10</f>
+        <v>279050</v>
+      </c>
+      <c r="V47" s="95">
+        <f t="shared" si="55"/>
+        <v>299420</v>
+      </c>
+      <c r="W47" s="81">
+        <f t="shared" ref="W47:X47" si="56">W4-W10</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X47" s="95">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G48" s="25" t="s">
         <v>40</v>
       </c>
       <c r="H48" s="26"/>
       <c r="I48" s="26"/>
       <c r="J48" s="26"/>
-      <c r="K48" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="L48" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="M48" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="N48" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="O48" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="P48" s="182" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q48" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="R48" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="S48" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="T48" s="57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="K48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="M48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="O48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="P48" s="161" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="R48" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="S48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="T48" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="U48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="V48" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="W48" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="X48" s="55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G49" s="27"/>
       <c r="H49" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
-      <c r="K49" s="168"/>
-      <c r="L49" s="60"/>
-      <c r="M49" s="168"/>
-      <c r="N49" s="60"/>
-      <c r="O49" s="58"/>
+      <c r="K49" s="147"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="147"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="56"/>
       <c r="P49" s="2"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="59"/>
-      <c r="S49" s="58"/>
-      <c r="T49" s="59"/>
-    </row>
-    <row r="50" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="Q49" s="56"/>
+      <c r="R49" s="57"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="57"/>
+      <c r="U49" s="56"/>
+      <c r="V49" s="57"/>
+      <c r="W49" s="56"/>
+      <c r="X49" s="57"/>
+    </row>
+    <row r="50" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G50" s="27"/>
       <c r="H50" s="5" t="s">
         <v>36</v>
       </c>
       <c r="I50" s="6"/>
       <c r="J50" s="6"/>
-      <c r="K50" s="73"/>
-      <c r="L50" s="74">
+      <c r="K50" s="70"/>
+      <c r="L50" s="71">
         <f>SUM(N51)</f>
         <v>135300</v>
       </c>
-      <c r="M50" s="73"/>
-      <c r="N50" s="74">
+      <c r="M50" s="70"/>
+      <c r="N50" s="71">
         <f>SUM(P51)</f>
         <v>135300</v>
       </c>
-      <c r="O50" s="91">
-        <f t="shared" ref="O50:T50" si="35">SUM(O51)</f>
+      <c r="O50" s="88">
+        <f t="shared" ref="O50:X50" si="57">SUM(O51)</f>
         <v>135300</v>
       </c>
-      <c r="P50" s="72">
-        <f t="shared" si="35"/>
+      <c r="P50" s="69">
+        <f t="shared" si="57"/>
         <v>135300</v>
       </c>
-      <c r="Q50" s="91">
-        <f t="shared" si="35"/>
+      <c r="Q50" s="88">
+        <f t="shared" si="57"/>
         <v>135300</v>
       </c>
-      <c r="R50" s="92">
-        <f t="shared" si="35"/>
+      <c r="R50" s="89">
+        <f t="shared" si="57"/>
         <v>135300</v>
       </c>
-      <c r="S50" s="91">
-        <f t="shared" si="35"/>
+      <c r="S50" s="88">
+        <f t="shared" si="57"/>
         <v>135300</v>
       </c>
-      <c r="T50" s="92">
-        <f t="shared" si="35"/>
+      <c r="T50" s="89">
+        <f t="shared" si="57"/>
+        <v>135300</v>
+      </c>
+      <c r="U50" s="88">
+        <f t="shared" si="57"/>
+        <v>135300</v>
+      </c>
+      <c r="V50" s="89">
+        <f t="shared" si="57"/>
+        <v>135300</v>
+      </c>
+      <c r="W50" s="88">
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X50" s="89">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G51" s="27"/>
       <c r="H51" s="7"/>
       <c r="I51" s="14" t="s">
         <v>26</v>
       </c>
       <c r="J51" s="15"/>
-      <c r="K51" s="161"/>
-      <c r="L51" s="78">
+      <c r="K51" s="140"/>
+      <c r="L51" s="75">
         <f>SUM(N52)</f>
         <v>135300</v>
       </c>
-      <c r="M51" s="161"/>
-      <c r="N51" s="78">
+      <c r="M51" s="140"/>
+      <c r="N51" s="75">
         <f>SUM(P52)</f>
         <v>135300</v>
       </c>
-      <c r="O51" s="77">
-        <f t="shared" ref="O51:T51" si="36">SUM(O52)</f>
+      <c r="O51" s="74">
+        <f t="shared" ref="O51:X51" si="58">SUM(O52)</f>
         <v>135300</v>
       </c>
-      <c r="P51" s="76">
-        <f t="shared" si="36"/>
+      <c r="P51" s="73">
+        <f t="shared" si="58"/>
         <v>135300</v>
       </c>
-      <c r="Q51" s="77">
-        <f t="shared" si="36"/>
+      <c r="Q51" s="74">
+        <f t="shared" si="58"/>
         <v>135300</v>
       </c>
-      <c r="R51" s="94">
-        <f t="shared" si="36"/>
+      <c r="R51" s="91">
+        <f t="shared" si="58"/>
         <v>135300</v>
       </c>
-      <c r="S51" s="77">
-        <f t="shared" si="36"/>
+      <c r="S51" s="74">
+        <f t="shared" si="58"/>
         <v>135300</v>
       </c>
-      <c r="T51" s="94">
-        <f t="shared" si="36"/>
+      <c r="T51" s="91">
+        <f t="shared" si="58"/>
+        <v>135300</v>
+      </c>
+      <c r="U51" s="74">
+        <f t="shared" si="58"/>
+        <v>135300</v>
+      </c>
+      <c r="V51" s="91">
+        <f t="shared" si="58"/>
+        <v>135300</v>
+      </c>
+      <c r="W51" s="74">
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X51" s="91">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G52" s="27"/>
       <c r="H52" s="7"/>
       <c r="I52" s="8"/>
       <c r="J52" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="164"/>
-      <c r="L52" s="177">
+      <c r="K52" s="143"/>
+      <c r="L52" s="156">
         <f>45100+45100+45100</f>
         <v>135300</v>
       </c>
-      <c r="M52" s="164"/>
-      <c r="N52" s="177">
+      <c r="M52" s="143"/>
+      <c r="N52" s="156">
         <f>45100+45100+45100</f>
         <v>135300</v>
       </c>
-      <c r="O52" s="96">
+      <c r="O52" s="93">
         <v>135300</v>
       </c>
-      <c r="P52" s="109">
+      <c r="P52" s="106">
         <f>45100+45100+45100</f>
         <v>135300</v>
       </c>
-      <c r="Q52" s="96">
+      <c r="Q52" s="93">
         <v>135300</v>
       </c>
-      <c r="R52" s="97">
+      <c r="R52" s="94">
         <v>135300</v>
       </c>
-      <c r="S52" s="96">
+      <c r="S52" s="93">
         <v>135300</v>
       </c>
-      <c r="T52" s="97"/>
-    </row>
-    <row r="53" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T52" s="94">
+        <f>45100+45100+45100</f>
+        <v>135300</v>
+      </c>
+      <c r="U52" s="93">
+        <v>135300</v>
+      </c>
+      <c r="V52" s="94">
+        <f>45100+45100+45100</f>
+        <v>135300</v>
+      </c>
+      <c r="W52" s="93"/>
+      <c r="X52" s="94"/>
+    </row>
+    <row r="53" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G53" s="28"/>
       <c r="H53" s="22" t="s">
         <v>37</v>
       </c>
       <c r="I53" s="23"/>
       <c r="J53" s="23"/>
-      <c r="K53" s="167"/>
-      <c r="L53" s="85">
+      <c r="K53" s="146"/>
+      <c r="L53" s="82">
         <f>N49-N50</f>
         <v>-135300</v>
       </c>
-      <c r="M53" s="167"/>
-      <c r="N53" s="85">
+      <c r="M53" s="146"/>
+      <c r="N53" s="82">
         <f>P49-P50</f>
         <v>-135300</v>
       </c>
-      <c r="O53" s="84">
-        <f t="shared" ref="O53:P53" si="37">O49-O50</f>
+      <c r="O53" s="81">
+        <f t="shared" ref="O53:P53" si="59">O49-O50</f>
         <v>-135300</v>
       </c>
-      <c r="P53" s="83">
-        <f t="shared" si="37"/>
+      <c r="P53" s="80">
+        <f t="shared" si="59"/>
         <v>-135300</v>
       </c>
-      <c r="Q53" s="84">
-        <f t="shared" ref="Q53:R53" si="38">Q49-Q50</f>
+      <c r="Q53" s="81">
+        <f t="shared" ref="Q53:R53" si="60">Q49-Q50</f>
         <v>-135300</v>
       </c>
-      <c r="R53" s="98">
-        <f t="shared" si="38"/>
+      <c r="R53" s="95">
+        <f t="shared" si="60"/>
         <v>-135300</v>
       </c>
-      <c r="S53" s="84">
-        <f t="shared" ref="S53:T53" si="39">S49-S50</f>
+      <c r="S53" s="81">
+        <f t="shared" ref="S53:T53" si="61">S49-S50</f>
         <v>-135300</v>
       </c>
-      <c r="T53" s="98">
-        <f t="shared" si="39"/>
+      <c r="T53" s="95">
+        <f t="shared" si="61"/>
+        <v>-135300</v>
+      </c>
+      <c r="U53" s="81">
+        <f t="shared" ref="U53:V53" si="62">U49-U50</f>
+        <v>-135300</v>
+      </c>
+      <c r="V53" s="95">
+        <f t="shared" si="62"/>
+        <v>-135300</v>
+      </c>
+      <c r="W53" s="81">
+        <f t="shared" ref="W53:X53" si="63">W49-W50</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X53" s="95">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G54" s="29" t="s">
         <v>41</v>
       </c>
       <c r="H54" s="26"/>
       <c r="I54" s="26"/>
       <c r="J54" s="26"/>
-      <c r="K54" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="L54" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="M54" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="N54" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="O54" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="P54" s="182" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q54" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="R54" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="S54" s="56" t="s">
-        <v>65</v>
-      </c>
-      <c r="T54" s="57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="K54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="L54" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="M54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="N54" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="O54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="P54" s="161" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="R54" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="S54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="T54" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="U54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="V54" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="W54" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="X54" s="55" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G55" s="27"/>
       <c r="H55" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
-      <c r="K55" s="168"/>
-      <c r="L55" s="178">
+      <c r="K55" s="147"/>
+      <c r="L55" s="157">
         <f>SUM(L56,L57)</f>
         <v>0</v>
       </c>
-      <c r="M55" s="168"/>
-      <c r="N55" s="178">
+      <c r="M55" s="147"/>
+      <c r="N55" s="157">
         <f>SUM(N56,N57)</f>
         <v>7000</v>
       </c>
-      <c r="O55" s="58">
-        <f t="shared" ref="O55:S55" si="40">SUM(O56)</f>
+      <c r="O55" s="56">
+        <f t="shared" ref="O55:Q55" si="64">SUM(O56)</f>
         <v>0</v>
       </c>
-      <c r="P55" s="198">
+      <c r="P55" s="173">
         <f>SUM(P56,P57)</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="58">
-        <f t="shared" si="40"/>
+      <c r="Q55" s="56">
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
-      <c r="R55" s="178">
+      <c r="R55" s="157">
         <f>SUM(R56,R57)</f>
         <v>0</v>
       </c>
-      <c r="S55" s="178">
+      <c r="S55" s="157">
         <f>SUM(S56,S57)</f>
         <v>730721</v>
       </c>
-      <c r="T55" s="178">
+      <c r="T55" s="157">
         <f>SUM(T56,T57)</f>
+        <v>681033</v>
+      </c>
+      <c r="U55" s="157">
+        <f>SUM(U56,U57)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="V55" s="157">
+        <f>SUM(V56,V57)</f>
+        <v>0</v>
+      </c>
+      <c r="W55" s="157">
+        <f>SUM(W56,W57)</f>
+        <v>0</v>
+      </c>
+      <c r="X55" s="157">
+        <f>SUM(X56,X57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G56" s="27"/>
       <c r="H56" s="3"/>
       <c r="I56" s="31" t="s">
         <v>44</v>
       </c>
       <c r="J56" s="17"/>
-      <c r="K56" s="158"/>
-      <c r="L56" s="179"/>
-      <c r="M56" s="158"/>
-      <c r="N56" s="179">
+      <c r="K56" s="137"/>
+      <c r="L56" s="158"/>
+      <c r="M56" s="137"/>
+      <c r="N56" s="158">
         <v>7000</v>
       </c>
-      <c r="O56" s="68"/>
-      <c r="P56" s="183"/>
-      <c r="Q56" s="68"/>
-      <c r="R56" s="69"/>
-      <c r="S56" s="68">
+      <c r="O56" s="65"/>
+      <c r="P56" s="162"/>
+      <c r="Q56" s="65"/>
+      <c r="R56" s="66"/>
+      <c r="S56" s="65">
         <f>50000</f>
         <v>50000</v>
       </c>
-      <c r="T56" s="69"/>
-    </row>
-    <row r="57" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T56" s="66"/>
+      <c r="U56" s="65"/>
+      <c r="V56" s="66"/>
+      <c r="W56" s="65"/>
+      <c r="X56" s="66"/>
+    </row>
+    <row r="57" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G57" s="27"/>
       <c r="H57" s="3"/>
       <c r="I57" s="16" t="s">
         <v>45</v>
       </c>
       <c r="J57" s="17"/>
-      <c r="K57" s="169"/>
-      <c r="L57" s="71"/>
-      <c r="M57" s="169"/>
-      <c r="N57" s="71"/>
-      <c r="O57" s="70"/>
-      <c r="P57" s="184"/>
-      <c r="Q57" s="70"/>
-      <c r="R57" s="71"/>
-      <c r="S57" s="70">
+      <c r="K57" s="148"/>
+      <c r="L57" s="68"/>
+      <c r="M57" s="148"/>
+      <c r="N57" s="68"/>
+      <c r="O57" s="67"/>
+      <c r="P57" s="163"/>
+      <c r="Q57" s="67"/>
+      <c r="R57" s="68"/>
+      <c r="S57" s="67">
         <f>238821+227235+214665</f>
         <v>680721</v>
       </c>
-      <c r="T57" s="71"/>
-    </row>
-    <row r="58" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T57" s="68">
+        <f>224620+217592+238821</f>
+        <v>681033</v>
+      </c>
+      <c r="U57" s="67"/>
+      <c r="V57" s="68"/>
+      <c r="W57" s="67"/>
+      <c r="X57" s="68"/>
+    </row>
+    <row r="58" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G58" s="27"/>
       <c r="H58" s="5" t="s">
         <v>36</v>
       </c>
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
-      <c r="K58" s="73"/>
-      <c r="L58" s="74">
+      <c r="K58" s="70"/>
+      <c r="L58" s="71">
         <f>SUM(L59,L60,L61)</f>
         <v>200000</v>
       </c>
-      <c r="M58" s="73"/>
-      <c r="N58" s="74">
+      <c r="M58" s="70"/>
+      <c r="N58" s="71">
         <f>SUM(N59,N60,N61)</f>
         <v>212000</v>
       </c>
-      <c r="O58" s="73">
+      <c r="O58" s="70">
         <f>SUM(O59,O60,O61)</f>
         <v>0</v>
       </c>
-      <c r="P58" s="75">
+      <c r="P58" s="72">
         <f>SUM(P59,P60,P61)</f>
         <v>210100</v>
       </c>
-      <c r="Q58" s="73">
-        <f t="shared" ref="Q58:T58" si="41">SUM(Q59,Q60,Q61)</f>
+      <c r="Q58" s="70">
+        <f t="shared" ref="Q58:T58" si="65">SUM(Q59,Q60,Q61)</f>
         <v>200000</v>
       </c>
-      <c r="R58" s="74">
+      <c r="R58" s="71">
         <f>SUM(R59,R60,R61)</f>
         <v>48800</v>
       </c>
-      <c r="S58" s="73">
-        <f t="shared" si="41"/>
+      <c r="S58" s="70">
+        <f t="shared" si="65"/>
         <v>1200000</v>
       </c>
-      <c r="T58" s="74">
-        <f t="shared" si="41"/>
+      <c r="T58" s="71">
+        <f t="shared" si="65"/>
+        <v>1150000</v>
+      </c>
+      <c r="U58" s="70">
+        <f>SUM(U59,U60,U61)</f>
+        <v>200000</v>
+      </c>
+      <c r="V58" s="71">
+        <f>SUM(V59,V60,V61)</f>
+        <v>122000</v>
+      </c>
+      <c r="W58" s="70">
+        <f t="shared" ref="W58:X58" si="66">SUM(W59,W60,W61)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X58" s="71">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G59" s="27"/>
       <c r="H59" s="7"/>
       <c r="I59" s="30" t="s">
         <v>43</v>
       </c>
       <c r="J59" s="15"/>
-      <c r="K59" s="161"/>
-      <c r="L59" s="78"/>
-      <c r="M59" s="161"/>
-      <c r="N59" s="78">
+      <c r="K59" s="140"/>
+      <c r="L59" s="75"/>
+      <c r="M59" s="140"/>
+      <c r="N59" s="75">
         <v>12000</v>
       </c>
-      <c r="O59" s="77"/>
-      <c r="P59" s="185">
+      <c r="O59" s="74"/>
+      <c r="P59" s="164">
         <v>10000</v>
       </c>
-      <c r="Q59" s="77"/>
-      <c r="R59" s="78">
+      <c r="Q59" s="74"/>
+      <c r="R59" s="75">
         <f>3000+11500+7000+12000+15000</f>
         <v>48500</v>
       </c>
-      <c r="S59" s="77"/>
-      <c r="T59" s="78"/>
-    </row>
-    <row r="60" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="S59" s="74"/>
+      <c r="T59" s="75">
+        <f>20000+15000+60000+30000+20000+5000</f>
+        <v>150000</v>
+      </c>
+      <c r="U59" s="74"/>
+      <c r="V59" s="75">
+        <v>122000</v>
+      </c>
+      <c r="W59" s="74"/>
+      <c r="X59" s="75"/>
+    </row>
+    <row r="60" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G60" s="27"/>
       <c r="H60" s="7"/>
       <c r="I60" s="30" t="s">
         <v>46</v>
       </c>
       <c r="J60" s="15"/>
-      <c r="K60" s="161"/>
-      <c r="L60" s="80">
+      <c r="K60" s="140"/>
+      <c r="L60" s="77">
         <v>200000</v>
       </c>
-      <c r="M60" s="161"/>
-      <c r="N60" s="80">
+      <c r="M60" s="140"/>
+      <c r="N60" s="77">
         <v>200000</v>
       </c>
-      <c r="O60" s="79"/>
-      <c r="P60" s="186">
+      <c r="O60" s="76"/>
+      <c r="P60" s="165">
         <v>200000</v>
       </c>
-      <c r="Q60" s="79">
+      <c r="Q60" s="76">
         <v>200000</v>
       </c>
-      <c r="R60" s="80"/>
-      <c r="S60" s="79">
+      <c r="R60" s="77"/>
+      <c r="S60" s="76">
         <v>1200000</v>
       </c>
-      <c r="T60" s="80"/>
-    </row>
-    <row r="61" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T60" s="77">
+        <v>1000000</v>
+      </c>
+      <c r="U60" s="76">
+        <v>200000</v>
+      </c>
+      <c r="V60" s="77"/>
+      <c r="W60" s="76"/>
+      <c r="X60" s="77"/>
+    </row>
+    <row r="61" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G61" s="27"/>
       <c r="H61" s="7"/>
       <c r="I61" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J61" s="15"/>
-      <c r="K61" s="166"/>
-      <c r="L61" s="80"/>
-      <c r="M61" s="166"/>
-      <c r="N61" s="80"/>
-      <c r="O61" s="81"/>
-      <c r="P61" s="187">
+      <c r="K61" s="145"/>
+      <c r="L61" s="77"/>
+      <c r="M61" s="145"/>
+      <c r="N61" s="77"/>
+      <c r="O61" s="78"/>
+      <c r="P61" s="166">
         <v>100</v>
       </c>
-      <c r="Q61" s="81"/>
-      <c r="R61" s="82">
+      <c r="Q61" s="78"/>
+      <c r="R61" s="79">
         <v>300</v>
       </c>
-      <c r="S61" s="81"/>
-      <c r="T61" s="82"/>
-    </row>
-    <row r="62" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="S61" s="78"/>
+      <c r="T61" s="79"/>
+      <c r="U61" s="78"/>
+      <c r="V61" s="79"/>
+      <c r="W61" s="78"/>
+      <c r="X61" s="79"/>
+    </row>
+    <row r="62" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G62" s="28"/>
       <c r="H62" s="22" t="s">
         <v>37</v>
       </c>
       <c r="I62" s="23"/>
       <c r="J62" s="23"/>
-      <c r="K62" s="167"/>
-      <c r="L62" s="85">
+      <c r="K62" s="146"/>
+      <c r="L62" s="82">
         <f>L55-L58</f>
         <v>-200000</v>
       </c>
-      <c r="M62" s="167"/>
-      <c r="N62" s="85">
+      <c r="M62" s="146"/>
+      <c r="N62" s="82">
         <f>N55-N58</f>
         <v>-205000</v>
       </c>
-      <c r="O62" s="84">
-        <f t="shared" ref="O62:T62" si="42">O55-O58</f>
+      <c r="O62" s="81">
+        <f t="shared" ref="O62:T62" si="67">O55-O58</f>
         <v>0</v>
       </c>
-      <c r="P62" s="188">
-        <f t="shared" si="42"/>
+      <c r="P62" s="167">
+        <f t="shared" si="67"/>
         <v>-210100</v>
       </c>
-      <c r="Q62" s="84">
-        <f t="shared" si="42"/>
+      <c r="Q62" s="81">
+        <f t="shared" si="67"/>
         <v>-200000</v>
       </c>
-      <c r="R62" s="85">
-        <f t="shared" si="42"/>
+      <c r="R62" s="82">
+        <f t="shared" si="67"/>
         <v>-48800</v>
       </c>
-      <c r="S62" s="84">
-        <f t="shared" si="42"/>
+      <c r="S62" s="81">
+        <f t="shared" si="67"/>
         <v>-469279</v>
       </c>
-      <c r="T62" s="85">
-        <f t="shared" si="42"/>
+      <c r="T62" s="82">
+        <f t="shared" si="67"/>
+        <v>-468967</v>
+      </c>
+      <c r="U62" s="81">
+        <f t="shared" ref="U62:V62" si="68">U55-U58</f>
+        <v>-200000</v>
+      </c>
+      <c r="V62" s="82">
+        <f t="shared" si="68"/>
+        <v>-122000</v>
+      </c>
+      <c r="W62" s="81">
+        <f t="shared" ref="W62:X62" si="69">W55-W58</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="X62" s="82">
+        <f t="shared" si="69"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G63" s="36" t="s">
         <v>50</v>
       </c>
       <c r="H63" s="37"/>
       <c r="I63" s="37"/>
       <c r="J63" s="37"/>
-      <c r="K63" s="170"/>
-      <c r="L63" s="87"/>
-      <c r="M63" s="170"/>
-      <c r="N63" s="87"/>
-      <c r="O63" s="86">
+      <c r="K63" s="149"/>
+      <c r="L63" s="84"/>
+      <c r="M63" s="149"/>
+      <c r="N63" s="84"/>
+      <c r="O63" s="83">
         <v>36</v>
       </c>
-      <c r="P63" s="189">
+      <c r="P63" s="168">
         <v>30297</v>
       </c>
-      <c r="Q63" s="86">
+      <c r="Q63" s="83">
         <v>85000</v>
       </c>
-      <c r="R63" s="87">
+      <c r="R63" s="84">
         <v>89600</v>
       </c>
-      <c r="S63" s="86">
+      <c r="S63" s="83">
         <v>257530</v>
       </c>
-      <c r="T63" s="87"/>
-    </row>
-    <row r="64" spans="7:20" x14ac:dyDescent="0.25">
+      <c r="T63" s="84">
+        <v>257530</v>
+      </c>
+      <c r="U63" s="83">
+        <v>125562</v>
+      </c>
+      <c r="V63" s="84">
+        <v>125562</v>
+      </c>
+      <c r="W63" s="83">
+        <v>257530</v>
+      </c>
+      <c r="X63" s="84">
+        <v>257530</v>
+      </c>
+    </row>
+    <row r="64" spans="7:24" x14ac:dyDescent="0.25">
       <c r="G64" s="38" t="s">
         <v>51</v>
       </c>
       <c r="H64" s="24"/>
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
-      <c r="K64" s="171"/>
-      <c r="L64" s="89"/>
-      <c r="M64" s="171"/>
-      <c r="N64" s="89"/>
-      <c r="O64" s="88">
-        <f t="shared" ref="O64:T64" si="43">SUM(O47,O53,O62)</f>
+      <c r="K64" s="150"/>
+      <c r="L64" s="86"/>
+      <c r="M64" s="150"/>
+      <c r="N64" s="86"/>
+      <c r="O64" s="85">
+        <f t="shared" ref="O64:T64" si="70">SUM(O47,O53,O62)</f>
         <v>205152</v>
       </c>
-      <c r="P64" s="190">
-        <f t="shared" si="43"/>
+      <c r="P64" s="169">
+        <f t="shared" si="70"/>
         <v>64703</v>
       </c>
-      <c r="Q64" s="88">
-        <f t="shared" si="43"/>
+      <c r="Q64" s="85">
+        <f t="shared" si="70"/>
         <v>108390</v>
       </c>
-      <c r="R64" s="89">
-        <f t="shared" si="43"/>
+      <c r="R64" s="86">
+        <f t="shared" si="70"/>
         <v>156830</v>
       </c>
-      <c r="S64" s="88">
-        <f t="shared" si="43"/>
+      <c r="S64" s="85">
+        <f t="shared" si="70"/>
         <v>-172539</v>
       </c>
-      <c r="T64" s="89">
-        <f t="shared" si="43"/>
+      <c r="T64" s="86">
+        <f t="shared" si="70"/>
+        <v>-151168</v>
+      </c>
+      <c r="U64" s="85">
+        <f t="shared" ref="U64:V64" si="71">SUM(U47,U53,U62)</f>
+        <v>-56250</v>
+      </c>
+      <c r="V64" s="86">
+        <f t="shared" si="71"/>
+        <v>42120</v>
+      </c>
+      <c r="W64" s="85">
+        <f t="shared" ref="W64:X64" si="72">SUM(W47,W53,W62)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="7:20" x14ac:dyDescent="0.25">
-      <c r="G65" s="196" t="s">
-        <v>115</v>
+      <c r="X64" s="86">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="7:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="172" t="s">
+        <v>102</v>
       </c>
       <c r="H65" s="24"/>
       <c r="I65" s="24"/>
       <c r="J65" s="24"/>
-      <c r="K65" s="171"/>
-      <c r="L65" s="89"/>
-      <c r="M65" s="171"/>
-      <c r="N65" s="89"/>
-      <c r="O65" s="88"/>
-      <c r="P65" s="190"/>
-      <c r="Q65" s="88"/>
-      <c r="R65" s="89">
+      <c r="K65" s="150"/>
+      <c r="L65" s="86"/>
+      <c r="M65" s="150"/>
+      <c r="N65" s="86"/>
+      <c r="O65" s="85"/>
+      <c r="P65" s="169"/>
+      <c r="Q65" s="85"/>
+      <c r="R65" s="86">
         <v>11100</v>
       </c>
-      <c r="S65" s="88"/>
-      <c r="T65" s="89"/>
-    </row>
-    <row r="66" spans="7:20" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S65" s="85"/>
+      <c r="T65" s="86">
+        <v>19200</v>
+      </c>
+      <c r="U65" s="85"/>
+      <c r="V65" s="86">
+        <v>-4000</v>
+      </c>
+      <c r="W65" s="85"/>
+      <c r="X65" s="86"/>
+    </row>
+    <row r="66" spans="7:24" ht="15" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G66" s="39" t="s">
         <v>52</v>
       </c>
       <c r="H66" s="40"/>
       <c r="I66" s="40"/>
       <c r="J66" s="40"/>
-      <c r="K66" s="172"/>
-      <c r="L66" s="90"/>
-      <c r="M66" s="172"/>
-      <c r="N66" s="90"/>
-      <c r="O66" s="191">
-        <f t="shared" ref="O66:Q66" si="44">SUM(O63:O65)</f>
+      <c r="K66" s="151"/>
+      <c r="L66" s="87"/>
+      <c r="M66" s="151"/>
+      <c r="N66" s="87"/>
+      <c r="O66" s="170">
+        <f t="shared" ref="O66:Q66" si="73">SUM(O63:O65)</f>
         <v>205188</v>
       </c>
-      <c r="P66" s="191">
-        <f t="shared" si="44"/>
+      <c r="P66" s="170">
+        <f t="shared" si="73"/>
         <v>95000</v>
       </c>
-      <c r="Q66" s="172">
-        <f t="shared" si="44"/>
+      <c r="Q66" s="151">
+        <f t="shared" si="73"/>
         <v>193390</v>
       </c>
-      <c r="R66" s="90">
+      <c r="R66" s="87">
         <f>SUM(R63:R65)</f>
         <v>257530</v>
       </c>
-      <c r="S66" s="172">
-        <f t="shared" ref="S66:T66" si="45">SUM(S63:S65)</f>
+      <c r="S66" s="151">
+        <f t="shared" ref="S66:T66" si="74">SUM(S63:S65)</f>
         <v>84991</v>
       </c>
-      <c r="T66" s="90">
-        <f t="shared" si="45"/>
-        <v>0</v>
+      <c r="T66" s="87">
+        <f t="shared" si="74"/>
+        <v>125562</v>
+      </c>
+      <c r="U66" s="151">
+        <f t="shared" ref="U66:V66" si="75">SUM(U63:U65)</f>
+        <v>69312</v>
+      </c>
+      <c r="V66" s="87">
+        <f t="shared" si="75"/>
+        <v>163682</v>
+      </c>
+      <c r="W66" s="151">
+        <f t="shared" ref="W66:X66" si="76">SUM(W63:W65)</f>
+        <v>257530</v>
+      </c>
+      <c r="X66" s="87">
+        <f t="shared" si="76"/>
+        <v>257530</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="13">
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="U2:V2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="G1:G2"/>
@@ -4592,312 +5622,257 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{579ACA63-EF1D-49ED-BEE4-4702B85AA33B}">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="H1:N34"/>
+  <dimension ref="H1:M33"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="11" width="6.42578125" customWidth="1"/>
     <col min="12" max="12" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J1" s="149" t="s">
+    <row r="1" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J1" s="190" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="151" t="s">
+      <c r="K1" s="192" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="145" t="s">
+      <c r="L1" s="194" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="42">
-        <v>2025</v>
-      </c>
-      <c r="N1" s="63">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J2" s="150"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="140" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="M1" s="177">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J2" s="191"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="195"/>
+      <c r="M2" s="178" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J3" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-    </row>
-    <row r="4" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="M3" s="42"/>
+    </row>
+    <row r="4" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J4" s="3"/>
       <c r="K4" s="16" t="s">
         <v>15</v>
       </c>
       <c r="L4" s="17"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-    </row>
-    <row r="5" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="M4" s="43"/>
+    </row>
+    <row r="5" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J5" s="3"/>
       <c r="K5" s="4"/>
       <c r="L5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="44">
         <v>11110000</v>
       </c>
-      <c r="N5" s="45">
-        <v>11110000</v>
-      </c>
-    </row>
-    <row r="6" spans="10:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J6" s="3"/>
-      <c r="K6" s="48" t="s">
+      <c r="K6" s="47" t="s">
         <v>57</v>
       </c>
       <c r="L6" s="17"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="53"/>
-    </row>
-    <row r="7" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="M6" s="52"/>
+    </row>
+    <row r="7" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="46">
-        <v>200000</v>
-      </c>
-      <c r="N7" s="46">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="8" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="L7" s="174" t="s">
+        <v>107</v>
+      </c>
+      <c r="M7" s="45">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="8" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="46">
-        <v>200000</v>
-      </c>
-      <c r="N8" s="46">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="9" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="K8" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="17"/>
+      <c r="M8" s="52"/>
+    </row>
+    <row r="9" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="46">
-        <v>200000</v>
-      </c>
-      <c r="N9" s="46">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="10" spans="10:14" x14ac:dyDescent="0.25">
+      <c r="L9" s="174" t="s">
+        <v>105</v>
+      </c>
+      <c r="M9" s="45">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="10" spans="10:13" x14ac:dyDescent="0.25">
       <c r="J10" s="3"/>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="4"/>
+      <c r="L10" s="176" t="s">
+        <v>106</v>
+      </c>
+      <c r="M10" s="44">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="51"/>
+      <c r="K11" s="127" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="124"/>
+      <c r="M11" s="125">
+        <f>SUM(M12:M14)</f>
+        <v>163381</v>
+      </c>
+    </row>
+    <row r="12" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="3"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="133" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="132">
+        <v>139841</v>
+      </c>
+    </row>
+    <row r="13" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="51"/>
+      <c r="K13" s="126"/>
+      <c r="L13" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" s="99">
+        <v>20088</v>
+      </c>
+    </row>
+    <row r="14" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J14" s="51"/>
+      <c r="K14" s="53"/>
+      <c r="L14" s="131" t="s">
+        <v>97</v>
+      </c>
+      <c r="M14" s="129">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="15" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J15" s="51"/>
+      <c r="K15" s="134" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" s="124"/>
+      <c r="M15" s="128"/>
+    </row>
+    <row r="16" spans="10:13" x14ac:dyDescent="0.25">
+      <c r="J16" s="51"/>
+      <c r="K16" s="126"/>
+      <c r="L16" s="130" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="45">
+        <f>222500+122000</f>
+        <v>344500</v>
+      </c>
+    </row>
+    <row r="17" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="J17" s="175"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="174" t="s">
+        <v>104</v>
+      </c>
+      <c r="M17" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="J18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="90"/>
+    </row>
+    <row r="19" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="J19" s="7"/>
+      <c r="K19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="15"/>
+      <c r="M19" s="63"/>
+    </row>
+    <row r="20" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="M20" s="46">
+        <v>8984520</v>
+      </c>
+    </row>
+    <row r="22" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
         <v>67</v>
       </c>
-      <c r="L10" s="17"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="133"/>
-    </row>
-    <row r="11" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="M11" s="46">
-        <v>100</v>
-      </c>
-      <c r="N11" s="134"/>
-    </row>
-    <row r="12" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="137" t="s">
-        <v>101</v>
-      </c>
-      <c r="M12" s="45"/>
-      <c r="N12" s="135">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="13" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J13" s="52"/>
-      <c r="K13" s="130" t="s">
+    </row>
+    <row r="23" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
         <v>69</v>
       </c>
-      <c r="L13" s="127"/>
-      <c r="M13" s="128">
-        <f>SUM(M14:M16)</f>
-        <v>89600</v>
-      </c>
-      <c r="N13" s="128">
-        <f>SUM(N14:N16)</f>
-        <v>257200</v>
-      </c>
-    </row>
-    <row r="14" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J14" s="3"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="141" t="s">
-        <v>103</v>
-      </c>
-      <c r="M14" s="138">
-        <v>60000</v>
-      </c>
-      <c r="N14" s="139">
-        <v>253000</v>
-      </c>
-    </row>
-    <row r="15" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J15" s="52"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="136" t="s">
-        <v>102</v>
-      </c>
-      <c r="M15" s="102">
-        <v>26000</v>
-      </c>
-      <c r="N15" s="134">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="16" spans="10:14" x14ac:dyDescent="0.25">
-      <c r="J16" s="52"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="137" t="s">
-        <v>104</v>
-      </c>
-      <c r="M16" s="132">
-        <v>3600</v>
-      </c>
-      <c r="N16" s="135">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="17" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="J17" s="52"/>
-      <c r="K17" s="142" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="127"/>
-      <c r="M17" s="131"/>
-      <c r="N17" s="133"/>
-    </row>
-    <row r="18" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="J18" s="52"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="136" t="s">
-        <v>106</v>
-      </c>
-      <c r="M18" s="46">
-        <v>10000</v>
-      </c>
-      <c r="N18" s="134">
-        <v>48500</v>
-      </c>
-    </row>
-    <row r="19" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="J19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="93"/>
-    </row>
-    <row r="20" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="J20" s="7"/>
-      <c r="K20" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="15"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-    </row>
-    <row r="21" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M21" s="47">
-        <v>9133293</v>
-      </c>
-      <c r="N21" s="47">
-        <v>9089977</v>
-      </c>
-    </row>
-    <row r="23" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="I23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="8:14" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26" spans="8:14" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H26" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="8:14" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H27" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="8:14" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="8:13" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H29" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="I31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="I30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="H32" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="8:14" x14ac:dyDescent="0.25">
-      <c r="H32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H34" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4922,28 +5897,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="C2" s="117">
+      <c r="C2" s="114">
         <v>44480</v>
       </c>
-      <c r="D2" s="117">
+      <c r="D2" s="114">
         <v>44662</v>
       </c>
-      <c r="E2" s="117">
+      <c r="E2" s="114">
         <v>44925</v>
       </c>
-      <c r="F2" s="117">
+      <c r="F2" s="114">
         <v>45170</v>
       </c>
-      <c r="G2" s="117">
+      <c r="G2" s="114">
         <v>45533</v>
       </c>
-      <c r="H2" s="117">
+      <c r="H2" s="114">
         <v>45839</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>63280</v>
@@ -4967,38 +5942,38 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="119">
+        <v>75</v>
+      </c>
+      <c r="D4" s="116">
         <f>D3/C3*100</f>
         <v>176.20101137800253</v>
       </c>
-      <c r="E4" s="119">
+      <c r="E4" s="116">
         <f t="shared" ref="E4:G4" si="0">E3/D3*100</f>
         <v>119.01345291479821</v>
       </c>
-      <c r="F4" s="119">
+      <c r="F4" s="116">
         <f t="shared" si="0"/>
         <v>121.32629992464206</v>
       </c>
-      <c r="G4" s="119">
+      <c r="G4" s="116">
         <f t="shared" si="0"/>
         <v>117.82608695652175</v>
       </c>
-      <c r="H4" s="118">
+      <c r="H4" s="115">
         <f>D4/100*E4/100*F4/100*G4/100*100</f>
         <v>299.77876106194697</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="119">
+        <v>76</v>
+      </c>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116">
         <f>H4/G8*100</f>
         <v>217.99556049862977</v>
       </c>
@@ -5014,1027 +5989,133 @@
         <v>2024</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="119">
+        <v>73</v>
+      </c>
+      <c r="C8" s="116">
         <v>109.7</v>
       </c>
-      <c r="D8" s="119">
+      <c r="D8" s="116">
         <v>111.8</v>
       </c>
-      <c r="E8" s="119">
+      <c r="E8" s="116">
         <v>107.4</v>
       </c>
-      <c r="F8" s="119">
+      <c r="F8" s="116">
         <v>104.4</v>
       </c>
-      <c r="G8" s="119">
+      <c r="G8" s="116">
         <f>C8/100*D8/100*E8/100*F8/100*100</f>
         <v>137.51599361759997</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="121"/>
-      <c r="C10" s="121">
+      <c r="B10" s="118"/>
+      <c r="C10" s="118">
         <v>2021</v>
       </c>
-      <c r="D10" s="121">
+      <c r="D10" s="118">
         <v>2022</v>
       </c>
-      <c r="E10" s="121">
+      <c r="E10" s="118">
         <v>2023</v>
       </c>
-      <c r="F10" s="121">
+      <c r="F10" s="118">
         <v>2024</v>
       </c>
-      <c r="G10" s="121">
+      <c r="G10" s="118">
         <v>2025</v>
       </c>
-      <c r="I10" s="121"/>
+      <c r="I10" s="118"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="121" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="121">
+      <c r="B11" s="118" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="118">
         <v>63280</v>
       </c>
-      <c r="D11" s="121">
+      <c r="D11" s="118">
         <v>132700</v>
       </c>
-      <c r="E11" s="121">
+      <c r="E11" s="118">
         <v>161000</v>
       </c>
-      <c r="F11" s="121">
+      <c r="F11" s="118">
         <v>189700</v>
       </c>
-      <c r="G11" s="121">
+      <c r="G11" s="118">
         <v>189700</v>
       </c>
-      <c r="I11" s="121"/>
+      <c r="I11" s="118"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="118">
+        <v>84</v>
+      </c>
+      <c r="C12" s="115">
         <f>C11/C15</f>
         <v>0.63513711403852757</v>
       </c>
-      <c r="D12" s="118">
+      <c r="D12" s="115">
         <f t="shared" ref="D12:G12" si="1">D11/D15</f>
         <v>0.99697309352186103</v>
       </c>
-      <c r="E12" s="118">
+      <c r="E12" s="115">
         <f t="shared" si="1"/>
         <v>0.99327834355227551</v>
       </c>
-      <c r="F12" s="118">
+      <c r="F12" s="115">
         <f t="shared" si="1"/>
         <v>0.96231235796761661</v>
       </c>
-      <c r="G12" s="118">
+      <c r="G12" s="115">
         <f t="shared" si="1"/>
         <v>0.8121657201675091</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="120">
+        <v>82</v>
+      </c>
+      <c r="C15" s="117">
         <v>99632.03</v>
       </c>
-      <c r="D15" s="120">
+      <c r="D15" s="117">
         <v>133102.89000000001</v>
       </c>
-      <c r="E15" s="120">
+      <c r="E15" s="117">
         <v>162089.51</v>
       </c>
-      <c r="F15" s="120">
+      <c r="F15" s="117">
         <v>197129.34</v>
       </c>
-      <c r="G15" s="120">
+      <c r="G15" s="117">
         <v>233573.02</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2926198D-F714-452A-A809-7E4F86A173AE}">
-  <dimension ref="A1:I55"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2021</v>
-      </c>
-      <c r="B2">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>96</v>
-      </c>
-      <c r="D2" s="118">
-        <f>C2/B2</f>
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2021</v>
-      </c>
-      <c r="H2" s="118">
-        <f>AVERAGE(D2:D11)</f>
-        <v>13.093463203463205</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2021</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>103</v>
-      </c>
-      <c r="D3" s="118">
-        <f t="shared" ref="D3:D55" si="0">C3/B3</f>
-        <v>11.444444444444445</v>
-      </c>
-      <c r="G3">
-        <v>2022</v>
-      </c>
-      <c r="H3" s="118">
-        <f>AVERAGE(D12:D21)</f>
-        <v>10.640740137055925</v>
-      </c>
-      <c r="I3" s="195">
-        <f>(H3-H2)/H2</f>
-        <v>-0.18732424174518916</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2021</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>117</v>
-      </c>
-      <c r="D4" s="118">
-        <f t="shared" si="0"/>
-        <v>10.636363636363637</v>
-      </c>
-      <c r="G4">
-        <v>2023</v>
-      </c>
-      <c r="H4" s="118">
-        <f>AVERAGE(D23:D33)</f>
-        <v>20.222508923824712</v>
-      </c>
-      <c r="I4" s="195">
-        <f t="shared" ref="I4:I6" si="1">(H4-H3)/H3</f>
-        <v>0.90047954027189192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2021</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>117</v>
-      </c>
-      <c r="D5" s="118">
-        <f t="shared" si="0"/>
-        <v>10.636363636363637</v>
-      </c>
-      <c r="G5">
-        <v>2024</v>
-      </c>
-      <c r="H5" s="118">
-        <f>AVERAGE(D34:D44)</f>
-        <v>22.622238204457453</v>
-      </c>
-      <c r="I5" s="195">
-        <f t="shared" si="1"/>
-        <v>0.11866624906297119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2021</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>98</v>
-      </c>
-      <c r="D6" s="118">
-        <f t="shared" si="0"/>
-        <v>10.888888888888889</v>
-      </c>
-      <c r="G6">
-        <v>2025</v>
-      </c>
-      <c r="H6" s="118">
-        <f>AVERAGE(D45:D55)</f>
-        <v>34.140705758887577</v>
-      </c>
-      <c r="I6" s="195">
-        <f t="shared" si="1"/>
-        <v>0.50916569131345024</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2021</v>
-      </c>
-      <c r="B7">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>124</v>
-      </c>
-      <c r="D7" s="118">
-        <f t="shared" si="0"/>
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2021</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>122</v>
-      </c>
-      <c r="D8" s="118">
-        <f t="shared" si="0"/>
-        <v>17.428571428571427</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>2021</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>69</v>
-      </c>
-      <c r="D9" s="118">
-        <f t="shared" si="0"/>
-        <v>17.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>2021</v>
-      </c>
-      <c r="B10">
-        <v>18</v>
-      </c>
-      <c r="C10">
-        <v>189</v>
-      </c>
-      <c r="D10" s="118">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>2021</v>
-      </c>
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11">
-        <v>142</v>
-      </c>
-      <c r="D11" s="118">
-        <f t="shared" si="0"/>
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>2022</v>
-      </c>
-      <c r="B12">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>181</v>
-      </c>
-      <c r="D12" s="118">
-        <f t="shared" si="0"/>
-        <v>9.526315789473685</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>2022</v>
-      </c>
-      <c r="B13">
-        <v>15</v>
-      </c>
-      <c r="C13">
-        <v>183</v>
-      </c>
-      <c r="D13" s="118">
-        <f t="shared" si="0"/>
-        <v>12.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14">
-        <v>18</v>
-      </c>
-      <c r="C14">
-        <v>240</v>
-      </c>
-      <c r="D14" s="118">
-        <f t="shared" si="0"/>
-        <v>13.333333333333334</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>2022</v>
-      </c>
-      <c r="B15">
-        <v>13</v>
-      </c>
-      <c r="C15">
-        <v>103</v>
-      </c>
-      <c r="D15" s="118">
-        <f t="shared" si="0"/>
-        <v>7.9230769230769234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2022</v>
-      </c>
-      <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>148</v>
-      </c>
-      <c r="D16" s="118">
-        <f t="shared" si="0"/>
-        <v>12.333333333333334</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>2022</v>
-      </c>
-      <c r="B17">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>246</v>
-      </c>
-      <c r="D17" s="118">
-        <f t="shared" si="0"/>
-        <v>11.181818181818182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2022</v>
-      </c>
-      <c r="B18">
-        <v>28</v>
-      </c>
-      <c r="C18">
-        <v>357</v>
-      </c>
-      <c r="D18" s="118">
-        <f t="shared" si="0"/>
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2022</v>
-      </c>
-      <c r="B19">
-        <v>15</v>
-      </c>
-      <c r="C19">
-        <v>169</v>
-      </c>
-      <c r="D19" s="118">
-        <f t="shared" si="0"/>
-        <v>11.266666666666667</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2022</v>
-      </c>
-      <c r="B20">
-        <v>14</v>
-      </c>
-      <c r="C20">
-        <v>16</v>
-      </c>
-      <c r="D20" s="118">
-        <f t="shared" si="0"/>
-        <v>1.1428571428571428</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2022</v>
-      </c>
-      <c r="B21">
-        <v>16</v>
-      </c>
-      <c r="C21">
-        <v>236</v>
-      </c>
-      <c r="D21" s="118">
-        <f t="shared" si="0"/>
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2022</v>
-      </c>
-      <c r="B22">
-        <v>23</v>
-      </c>
-      <c r="C22">
-        <v>182</v>
-      </c>
-      <c r="D22" s="118">
-        <f t="shared" si="0"/>
-        <v>7.9130434782608692</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2023</v>
-      </c>
-      <c r="B23">
-        <v>8</v>
-      </c>
-      <c r="C23">
-        <v>238</v>
-      </c>
-      <c r="D23" s="118">
-        <f t="shared" si="0"/>
-        <v>29.75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2023</v>
-      </c>
-      <c r="B24">
-        <v>19</v>
-      </c>
-      <c r="C24">
-        <v>334</v>
-      </c>
-      <c r="D24" s="118">
-        <f t="shared" si="0"/>
-        <v>17.578947368421051</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2023</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25">
-        <v>323</v>
-      </c>
-      <c r="D25" s="118">
-        <f t="shared" si="0"/>
-        <v>13.458333333333334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2023</v>
-      </c>
-      <c r="B26">
-        <v>9</v>
-      </c>
-      <c r="C26">
-        <v>182</v>
-      </c>
-      <c r="D26" s="118">
-        <f t="shared" si="0"/>
-        <v>20.222222222222221</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2023</v>
-      </c>
-      <c r="B27">
-        <v>20</v>
-      </c>
-      <c r="C27">
-        <v>242</v>
-      </c>
-      <c r="D27" s="118">
-        <f t="shared" si="0"/>
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2023</v>
-      </c>
-      <c r="B28">
-        <v>15</v>
-      </c>
-      <c r="C28">
-        <v>276</v>
-      </c>
-      <c r="D28" s="118">
-        <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2023</v>
-      </c>
-      <c r="B29">
-        <v>21</v>
-      </c>
-      <c r="C29">
-        <v>271</v>
-      </c>
-      <c r="D29" s="118">
-        <f t="shared" si="0"/>
-        <v>12.904761904761905</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2023</v>
-      </c>
-      <c r="B30">
-        <v>14</v>
-      </c>
-      <c r="C30">
-        <v>242</v>
-      </c>
-      <c r="D30" s="118">
-        <f t="shared" si="0"/>
-        <v>17.285714285714285</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2023</v>
-      </c>
-      <c r="B31">
-        <v>15</v>
-      </c>
-      <c r="C31">
-        <v>318</v>
-      </c>
-      <c r="D31" s="118">
-        <f t="shared" si="0"/>
-        <v>21.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2023</v>
-      </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
-      <c r="C32">
-        <v>201</v>
-      </c>
-      <c r="D32" s="118">
-        <f t="shared" si="0"/>
-        <v>28.714285714285715</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2023</v>
-      </c>
-      <c r="B33">
-        <v>6</v>
-      </c>
-      <c r="C33">
-        <v>185</v>
-      </c>
-      <c r="D33" s="118">
-        <f t="shared" si="0"/>
-        <v>30.833333333333332</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>2024</v>
-      </c>
-      <c r="B34">
-        <v>8</v>
-      </c>
-      <c r="C34">
-        <v>237</v>
-      </c>
-      <c r="D34" s="118">
-        <f t="shared" si="0"/>
-        <v>29.625</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>2024</v>
-      </c>
-      <c r="B35">
-        <v>17</v>
-      </c>
-      <c r="C35">
-        <v>441</v>
-      </c>
-      <c r="D35" s="118">
-        <f t="shared" si="0"/>
-        <v>25.941176470588236</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2024</v>
-      </c>
-      <c r="B36">
-        <v>21</v>
-      </c>
-      <c r="C36">
-        <v>355</v>
-      </c>
-      <c r="D36" s="118">
-        <f t="shared" si="0"/>
-        <v>16.904761904761905</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2024</v>
-      </c>
-      <c r="B37">
-        <v>14</v>
-      </c>
-      <c r="C37">
-        <v>375</v>
-      </c>
-      <c r="D37" s="118">
-        <f t="shared" si="0"/>
-        <v>26.785714285714285</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>2024</v>
-      </c>
-      <c r="B38">
-        <v>18</v>
-      </c>
-      <c r="C38">
-        <v>362</v>
-      </c>
-      <c r="D38" s="118">
-        <f t="shared" si="0"/>
-        <v>20.111111111111111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>2024</v>
-      </c>
-      <c r="B39">
-        <v>21</v>
-      </c>
-      <c r="C39">
-        <v>341</v>
-      </c>
-      <c r="D39" s="118">
-        <f t="shared" si="0"/>
-        <v>16.238095238095237</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2024</v>
-      </c>
-      <c r="B40">
-        <v>10</v>
-      </c>
-      <c r="C40">
-        <v>355</v>
-      </c>
-      <c r="D40" s="118">
-        <f t="shared" si="0"/>
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2024</v>
-      </c>
-      <c r="B41">
-        <v>21</v>
-      </c>
-      <c r="C41">
-        <v>505</v>
-      </c>
-      <c r="D41" s="118">
-        <f t="shared" si="0"/>
-        <v>24.047619047619047</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>2024</v>
-      </c>
-      <c r="B42">
-        <v>13</v>
-      </c>
-      <c r="C42">
-        <v>229</v>
-      </c>
-      <c r="D42" s="118">
-        <f t="shared" si="0"/>
-        <v>17.615384615384617</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>2024</v>
-      </c>
-      <c r="B43">
-        <v>11</v>
-      </c>
-      <c r="C43">
-        <v>230</v>
-      </c>
-      <c r="D43" s="118">
-        <f t="shared" si="0"/>
-        <v>20.90909090909091</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>2024</v>
-      </c>
-      <c r="B44">
-        <v>12</v>
-      </c>
-      <c r="C44">
-        <v>182</v>
-      </c>
-      <c r="D44" s="118">
-        <f t="shared" si="0"/>
-        <v>15.166666666666666</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>2025</v>
-      </c>
-      <c r="B45">
-        <v>9</v>
-      </c>
-      <c r="C45">
-        <v>181</v>
-      </c>
-      <c r="D45" s="118">
-        <f t="shared" si="0"/>
-        <v>20.111111111111111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>2025</v>
-      </c>
-      <c r="B46">
-        <v>18</v>
-      </c>
-      <c r="C46">
-        <v>320</v>
-      </c>
-      <c r="D46" s="118">
-        <f t="shared" si="0"/>
-        <v>17.777777777777779</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>2025</v>
-      </c>
-      <c r="B47">
-        <v>22</v>
-      </c>
-      <c r="C47">
-        <v>635</v>
-      </c>
-      <c r="D47" s="118">
-        <f t="shared" si="0"/>
-        <v>28.863636363636363</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>2025</v>
-      </c>
-      <c r="B48">
-        <v>15</v>
-      </c>
-      <c r="C48">
-        <v>535</v>
-      </c>
-      <c r="D48" s="118">
-        <f t="shared" si="0"/>
-        <v>35.666666666666664</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>2025</v>
-      </c>
-      <c r="B49">
-        <v>10</v>
-      </c>
-      <c r="C49">
-        <v>436</v>
-      </c>
-      <c r="D49" s="118">
-        <f t="shared" si="0"/>
-        <v>43.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>2025</v>
-      </c>
-      <c r="B50">
-        <v>14</v>
-      </c>
-      <c r="C50">
-        <v>373</v>
-      </c>
-      <c r="D50" s="118">
-        <f t="shared" si="0"/>
-        <v>26.642857142857142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>2025</v>
-      </c>
-      <c r="B51">
-        <v>14</v>
-      </c>
-      <c r="C51">
-        <v>505</v>
-      </c>
-      <c r="D51" s="118">
-        <f t="shared" si="0"/>
-        <v>36.071428571428569</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>2025</v>
-      </c>
-      <c r="B52">
-        <v>14</v>
-      </c>
-      <c r="C52">
-        <v>311</v>
-      </c>
-      <c r="D52" s="118">
-        <f t="shared" si="0"/>
-        <v>22.214285714285715</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>2025</v>
-      </c>
-      <c r="B53">
-        <v>5</v>
-      </c>
-      <c r="C53">
-        <v>110</v>
-      </c>
-      <c r="D53" s="118">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>2025</v>
-      </c>
-      <c r="B54">
-        <v>3</v>
-      </c>
-      <c r="C54">
-        <v>239</v>
-      </c>
-      <c r="D54" s="118">
-        <f t="shared" si="0"/>
-        <v>79.666666666666671</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>2025</v>
-      </c>
-      <c r="B55">
-        <v>15</v>
-      </c>
-      <c r="C55">
-        <v>644</v>
-      </c>
-      <c r="D55" s="118">
-        <f t="shared" si="0"/>
-        <v>42.93333333333333</v>
       </c>
     </row>
   </sheetData>
